--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_ADJR2.xlsx
@@ -1,217 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +27,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,68 +52,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -358,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -390,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -425,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -601,2378 +350,2485 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="14" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>-4.9685235080517108E-2</v>
+        <v>-0.05290805228241284</v>
       </c>
       <c r="C2">
-        <v>-9.3995073104699886E-2</v>
+        <v>-0.09443372468019953</v>
       </c>
       <c r="D2">
-        <v>-9.1108951820758247E-2</v>
+        <v>-0.09126380938006118</v>
       </c>
       <c r="E2">
-        <v>-7.8718176775406393E-2</v>
+        <v>-0.07399877926477888</v>
       </c>
       <c r="F2">
-        <v>-9.723203260975595E-2</v>
+        <v>-0.09241042489189454</v>
       </c>
       <c r="G2">
-        <v>-0.102552183115677</v>
+        <v>-0.09754132334002058</v>
       </c>
       <c r="H2">
-        <v>-3.5288128444634637E-2</v>
+        <v>-0.03574552227493137</v>
       </c>
       <c r="I2">
-        <v>1.9141869028561971E-2</v>
+        <v>0.02164721650338609</v>
       </c>
       <c r="J2">
-        <v>-2.2650629226171441E-2</v>
+        <v>-0.015063840528667</v>
       </c>
       <c r="K2">
-        <v>2.7277147680143311E-2</v>
+        <v>0.02926372003213416</v>
       </c>
       <c r="L2">
-        <v>0.1195800073381368</v>
+        <v>0.1126649665114977</v>
       </c>
       <c r="M2">
-        <v>0.14448555136842459</v>
+        <v>0.1431542778907424</v>
       </c>
       <c r="N2">
-        <v>0.25103595399697559</v>
+        <v>0.2506907001058479</v>
       </c>
       <c r="O2">
-        <v>0.33898672935219443</v>
+        <v>0.3376380698596818</v>
       </c>
       <c r="P2">
-        <v>0.37720054065633679</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.3788698974968248</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>-2.1496991682709739E-2</v>
+        <v>-0.02338977500364611</v>
       </c>
       <c r="C3">
-        <v>-0.19553524369805439</v>
+        <v>-0.2005140104515762</v>
       </c>
       <c r="D3">
-        <v>-0.13439763853215339</v>
+        <v>-0.1336381738029376</v>
       </c>
       <c r="E3">
-        <v>1.064913253867447E-2</v>
+        <v>0.01189838638913479</v>
       </c>
       <c r="F3">
-        <v>8.8537518129814211E-2</v>
+        <v>0.09657643833166271</v>
       </c>
       <c r="G3">
-        <v>0.15270819643194691</v>
+        <v>0.1503446018135401</v>
       </c>
       <c r="H3">
-        <v>0.21388693382188231</v>
+        <v>0.2068370342305458</v>
       </c>
       <c r="I3">
-        <v>0.24101757296216289</v>
+        <v>0.2308688696167036</v>
       </c>
       <c r="J3">
-        <v>0.2908458112878135</v>
+        <v>0.2770922267672325</v>
       </c>
       <c r="K3">
-        <v>0.32599206796935309</v>
+        <v>0.3085641985620685</v>
       </c>
       <c r="L3">
-        <v>0.31452570649010431</v>
+        <v>0.3038172183834741</v>
       </c>
       <c r="M3">
-        <v>0.31401006271918319</v>
+        <v>0.3001693282739456</v>
       </c>
       <c r="N3">
-        <v>0.28416644105696248</v>
+        <v>0.2718381996675008</v>
       </c>
       <c r="O3">
-        <v>0.26258514565358998</v>
+        <v>0.2618310565870506</v>
       </c>
       <c r="P3">
-        <v>0.28014841285636699</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.279503503517157</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>-4.3628622121103328E-2</v>
+        <v>-0.04284669174203476</v>
       </c>
       <c r="C4">
-        <v>-6.7992770698319077E-2</v>
+        <v>-0.06111144707903767</v>
       </c>
       <c r="D4">
-        <v>-0.1446472615676902</v>
+        <v>-0.1360344163531771</v>
       </c>
       <c r="E4">
-        <v>-0.1523465788956056</v>
+        <v>-0.1330592574692104</v>
       </c>
       <c r="F4">
-        <v>-0.2094964035175354</v>
+        <v>-0.190699294789714</v>
       </c>
       <c r="G4">
-        <v>-9.08866032552164E-2</v>
+        <v>-0.08282408736231267</v>
       </c>
       <c r="H4">
-        <v>-4.2229003320246403E-3</v>
+        <v>0.01328630784015385</v>
       </c>
       <c r="I4">
-        <v>4.2367162514714042E-2</v>
+        <v>0.05917543654447908</v>
       </c>
       <c r="J4">
-        <v>4.9159031277618302E-2</v>
+        <v>0.06003981550784638</v>
       </c>
       <c r="K4">
-        <v>0.13221266246002619</v>
+        <v>0.1288913429481977</v>
       </c>
       <c r="L4">
-        <v>0.20180420445747729</v>
+        <v>0.2039273894455753</v>
       </c>
       <c r="M4">
-        <v>0.26882604202165511</v>
+        <v>0.2686259895627419</v>
       </c>
       <c r="N4">
-        <v>0.29968424890304418</v>
+        <v>0.3006960808422869</v>
       </c>
       <c r="O4">
-        <v>0.30256968586007083</v>
+        <v>0.3044819192176816</v>
       </c>
       <c r="P4">
-        <v>0.28380315551617658</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.2883521766904626</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>-3.2648194467335148E-2</v>
+        <v>-0.03312243053805322</v>
       </c>
       <c r="C5">
-        <v>-9.5565187794171683E-2</v>
+        <v>-0.1079856605714666</v>
       </c>
       <c r="D5">
-        <v>-5.7767285381953172E-2</v>
+        <v>-0.05459503733835094</v>
       </c>
       <c r="E5">
-        <v>-0.15602085314316011</v>
+        <v>-0.1533703686752588</v>
       </c>
       <c r="F5">
-        <v>4.7812965373866617E-2</v>
+        <v>0.04500865097458354</v>
       </c>
       <c r="G5">
-        <v>0.14653747361741509</v>
+        <v>0.1400691270995831</v>
       </c>
       <c r="H5">
-        <v>0.17478190495539431</v>
+        <v>0.1693533787621279</v>
       </c>
       <c r="I5">
-        <v>0.24378630634543211</v>
+        <v>0.2433539035224793</v>
       </c>
       <c r="J5">
-        <v>0.32281333914007931</v>
+        <v>0.3180588361562026</v>
       </c>
       <c r="K5">
-        <v>0.35202227451379431</v>
+        <v>0.3489745368898847</v>
       </c>
       <c r="L5">
-        <v>0.38670271908465242</v>
+        <v>0.3763020465304757</v>
       </c>
       <c r="M5">
-        <v>0.38962130231524572</v>
+        <v>0.3728807720822171</v>
       </c>
       <c r="N5">
-        <v>0.36791791884215491</v>
+        <v>0.3450381085123029</v>
       </c>
       <c r="O5">
-        <v>0.34875919326653498</v>
+        <v>0.3228496262300383</v>
       </c>
       <c r="P5">
-        <v>0.31952703330371179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.2982882160189979</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>-3.3920285549120757E-2</v>
+        <v>-0.0412546801920514</v>
       </c>
       <c r="C6">
-        <v>-0.1224516319158071</v>
+        <v>-0.1260005161593281</v>
       </c>
       <c r="D6">
-        <v>-7.2342983769902391E-2</v>
+        <v>-0.07472468280652299</v>
       </c>
       <c r="E6">
-        <v>-0.1072916760757278</v>
+        <v>-0.1059164955041367</v>
       </c>
       <c r="F6">
-        <v>0.11336926204315929</v>
+        <v>0.1220747841336962</v>
       </c>
       <c r="G6">
-        <v>0.20479974728140241</v>
+        <v>0.2161262494102474</v>
       </c>
       <c r="H6">
-        <v>0.25590535130775399</v>
+        <v>0.274625959075315</v>
       </c>
       <c r="I6">
-        <v>0.33362770954523868</v>
+        <v>0.3459763203635748</v>
       </c>
       <c r="J6">
-        <v>0.37807976965642881</v>
+        <v>0.3881054825802098</v>
       </c>
       <c r="K6">
-        <v>0.39202568402784332</v>
+        <v>0.4035709836089361</v>
       </c>
       <c r="L6">
-        <v>0.41125340480224543</v>
+        <v>0.4237128868756384</v>
       </c>
       <c r="M6">
-        <v>0.41941973043136122</v>
+        <v>0.4230675376690948</v>
       </c>
       <c r="N6">
-        <v>0.40951717778866359</v>
+        <v>0.4141939030950981</v>
       </c>
       <c r="O6">
-        <v>0.41383397712959219</v>
+        <v>0.4177925070200631</v>
       </c>
       <c r="P6">
-        <v>0.39125412297377449</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.3980682099023356</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>-4.4421799230516631E-2</v>
+        <v>-0.04909751690350869</v>
       </c>
       <c r="C7">
-        <v>-6.4779510689083039E-2</v>
+        <v>-0.07368020058378556</v>
       </c>
       <c r="D7">
-        <v>-0.13295035909097599</v>
+        <v>-0.1418812321450352</v>
       </c>
       <c r="E7">
-        <v>-0.15631179643730739</v>
+        <v>-0.1669177695781892</v>
       </c>
       <c r="F7">
-        <v>-0.22426392784342461</v>
+        <v>-0.2299105953192489</v>
       </c>
       <c r="G7">
-        <v>-0.17506981745473721</v>
+        <v>-0.1833269736810698</v>
       </c>
       <c r="H7">
-        <v>-5.1808404396215549E-2</v>
+        <v>-0.06090437602934787</v>
       </c>
       <c r="I7">
-        <v>2.935367732327071E-2</v>
+        <v>0.03096514335234958</v>
       </c>
       <c r="J7">
-        <v>6.1436673384969498E-2</v>
+        <v>0.05937293358241082</v>
       </c>
       <c r="K7">
-        <v>8.2994021816217595E-2</v>
+        <v>0.07702919702022824</v>
       </c>
       <c r="L7">
-        <v>0.18045246401766971</v>
+        <v>0.1663863395715355</v>
       </c>
       <c r="M7">
-        <v>0.2543230709214801</v>
+        <v>0.2416368530020359</v>
       </c>
       <c r="N7">
-        <v>0.30202836556385809</v>
+        <v>0.2913360647965413</v>
       </c>
       <c r="O7">
-        <v>0.32250492766713801</v>
+        <v>0.3198451662837478</v>
       </c>
       <c r="P7">
-        <v>0.32860396245925672</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.3248471767528829</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>-4.159546219105259E-2</v>
+        <v>-0.04161676453248281</v>
       </c>
       <c r="C8">
-        <v>-7.3314979312563769E-2</v>
+        <v>-0.07057973858627367</v>
       </c>
       <c r="D8">
-        <v>-0.15058749050958861</v>
+        <v>-0.1416418503408551</v>
       </c>
       <c r="E8">
-        <v>-0.18897846677306701</v>
+        <v>-0.1841140903868617</v>
       </c>
       <c r="F8">
-        <v>-0.1281001324079421</v>
+        <v>-0.1166499923587756</v>
       </c>
       <c r="G8">
-        <v>-8.7148563225569499E-3</v>
+        <v>-0.01159558520438104</v>
       </c>
       <c r="H8">
-        <v>7.9651172281541057E-3</v>
+        <v>0.002520041407645938</v>
       </c>
       <c r="I8">
-        <v>0.10683987181253179</v>
+        <v>0.1065358913817624</v>
       </c>
       <c r="J8">
-        <v>0.15407877859611571</v>
+        <v>0.1443665198856982</v>
       </c>
       <c r="K8">
-        <v>0.26817023820025809</v>
+        <v>0.2649601125690924</v>
       </c>
       <c r="L8">
-        <v>0.27671848134202648</v>
+        <v>0.2852794860959212</v>
       </c>
       <c r="M8">
-        <v>0.32878623032641852</v>
+        <v>0.3309250211665597</v>
       </c>
       <c r="N8">
-        <v>0.35622465877809578</v>
+        <v>0.3553589923148683</v>
       </c>
       <c r="O8">
-        <v>0.3547553571528102</v>
+        <v>0.3554175993741479</v>
       </c>
       <c r="P8">
-        <v>0.34179546482013751</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.3380462752054358</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>-3.8672054981212102E-2</v>
+        <v>-0.03607211251945654</v>
       </c>
       <c r="C9">
-        <v>-6.6532765264412916E-2</v>
+        <v>-0.06618608712226508</v>
       </c>
       <c r="D9">
-        <v>-0.13247604734065449</v>
+        <v>-0.1340323915188791</v>
       </c>
       <c r="E9">
-        <v>-0.15886293236167801</v>
+        <v>-0.1582107314652124</v>
       </c>
       <c r="F9">
-        <v>-0.106308496468207</v>
+        <v>-0.1084794204748157</v>
       </c>
       <c r="G9">
-        <v>-2.3044386468857722E-3</v>
+        <v>-0.002529489497045312</v>
       </c>
       <c r="H9">
-        <v>5.7325553095061753E-3</v>
+        <v>0.01234063892225977</v>
       </c>
       <c r="I9">
-        <v>0.10586011007333521</v>
+        <v>0.1110449185537352</v>
       </c>
       <c r="J9">
-        <v>0.1398038324123678</v>
+        <v>0.1419693006268329</v>
       </c>
       <c r="K9">
-        <v>0.28861825136046498</v>
+        <v>0.2950826625093017</v>
       </c>
       <c r="L9">
-        <v>0.28474879327546587</v>
+        <v>0.2914990300899696</v>
       </c>
       <c r="M9">
-        <v>0.33129573996992723</v>
+        <v>0.3361571278411464</v>
       </c>
       <c r="N9">
-        <v>0.35868840336898039</v>
+        <v>0.3652434933016384</v>
       </c>
       <c r="O9">
-        <v>0.35779904404376911</v>
+        <v>0.3584917404340695</v>
       </c>
       <c r="P9">
-        <v>0.35630093144919839</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3574368941203659</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>-4.3015916699960639E-2</v>
+        <v>-0.04436179603757923</v>
       </c>
       <c r="C10">
-        <v>-7.3575320054658278E-2</v>
+        <v>-0.06975792298954113</v>
       </c>
       <c r="D10">
-        <v>-0.13911198852378079</v>
+        <v>-0.1358701835681856</v>
       </c>
       <c r="E10">
-        <v>-0.1742037364811958</v>
+        <v>-0.1686031173526271</v>
       </c>
       <c r="F10">
-        <v>-0.12377843402283981</v>
+        <v>-0.1147508276794302</v>
       </c>
       <c r="G10">
-        <v>-1.173953861749266E-2</v>
+        <v>-0.01438681787367522</v>
       </c>
       <c r="H10">
-        <v>-9.0022550046508425E-4</v>
+        <v>0.007647179935099677</v>
       </c>
       <c r="I10">
-        <v>0.1062441490937972</v>
+        <v>0.10059765577667</v>
       </c>
       <c r="J10">
-        <v>0.12924505731407379</v>
+        <v>0.1275128425245541</v>
       </c>
       <c r="K10">
-        <v>0.28193632310257771</v>
+        <v>0.2922363191494185</v>
       </c>
       <c r="L10">
-        <v>0.27036972650684049</v>
+        <v>0.2738511236655062</v>
       </c>
       <c r="M10">
-        <v>0.31153638295210617</v>
+        <v>0.3191006949597484</v>
       </c>
       <c r="N10">
-        <v>0.33603832931667438</v>
+        <v>0.3520255984220851</v>
       </c>
       <c r="O10">
-        <v>0.33368823972436501</v>
+        <v>0.3425410242127466</v>
       </c>
       <c r="P10">
-        <v>0.33452259375946419</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3450864745727094</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>-3.9968684129271313E-2</v>
+        <v>-0.03969628540689529</v>
       </c>
       <c r="C11">
-        <v>-6.8108792129805779E-2</v>
+        <v>-0.07027569620302593</v>
       </c>
       <c r="D11">
-        <v>-0.13767083737910191</v>
+        <v>-0.1420095071475113</v>
       </c>
       <c r="E11">
-        <v>-0.15962528847983931</v>
+        <v>-0.1789542672539678</v>
       </c>
       <c r="F11">
-        <v>-0.1186330717891616</v>
+        <v>-0.1265133851181932</v>
       </c>
       <c r="G11">
-        <v>-1.1797533167314529E-2</v>
+        <v>-0.01177472964020428</v>
       </c>
       <c r="H11">
-        <v>-5.7441998703305942E-3</v>
+        <v>-0.006069604479411682</v>
       </c>
       <c r="I11">
-        <v>9.8635376721562182E-2</v>
+        <v>0.1025672093118002</v>
       </c>
       <c r="J11">
-        <v>0.12857805062517799</v>
+        <v>0.1346634198528262</v>
       </c>
       <c r="K11">
-        <v>0.28829624051053759</v>
+        <v>0.2911464398552266</v>
       </c>
       <c r="L11">
-        <v>0.29317657418974702</v>
+        <v>0.2935264437604828</v>
       </c>
       <c r="M11">
-        <v>0.33868749095494077</v>
+        <v>0.3355304121454215</v>
       </c>
       <c r="N11">
-        <v>0.36477538977196211</v>
+        <v>0.3584664162819912</v>
       </c>
       <c r="O11">
-        <v>0.35820812150595799</v>
+        <v>0.3547477660320678</v>
       </c>
       <c r="P11">
-        <v>0.3584260933329389</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3515386512891138</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>-3.929677693920236E-2</v>
+        <v>-0.03463079357810216</v>
       </c>
       <c r="C12">
-        <v>-0.10495351173705229</v>
+        <v>-0.1078839043058302</v>
       </c>
       <c r="D12">
-        <v>-5.9800742629341527E-2</v>
+        <v>-0.05417091129565033</v>
       </c>
       <c r="E12">
-        <v>-0.14532154344103659</v>
+        <v>-0.1577660157634831</v>
       </c>
       <c r="F12">
-        <v>4.1629951308627573E-2</v>
+        <v>0.02697042290836315</v>
       </c>
       <c r="G12">
-        <v>9.8620629371537871E-2</v>
+        <v>0.09240585211540442</v>
       </c>
       <c r="H12">
-        <v>0.2085839343458317</v>
+        <v>0.2017873445031117</v>
       </c>
       <c r="I12">
-        <v>0.31345941049368348</v>
+        <v>0.3139854298249561</v>
       </c>
       <c r="J12">
-        <v>0.37375803978012612</v>
+        <v>0.3752649026421078</v>
       </c>
       <c r="K12">
-        <v>0.40394513963206091</v>
+        <v>0.4056492773492207</v>
       </c>
       <c r="L12">
-        <v>0.43446039628002647</v>
+        <v>0.4381332842070349</v>
       </c>
       <c r="M12">
-        <v>0.43886293885595512</v>
+        <v>0.4418204208437044</v>
       </c>
       <c r="N12">
-        <v>0.41807742203745302</v>
+        <v>0.4232338586271515</v>
       </c>
       <c r="O12">
-        <v>0.39751807582610438</v>
+        <v>0.400803670778786</v>
       </c>
       <c r="P12">
-        <v>0.35844988100897729</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.3663172775784369</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>-4.4655057381580723E-2</v>
+        <v>-0.04913895576458739</v>
       </c>
       <c r="C13">
-        <v>-0.18681809188177789</v>
+        <v>-0.1894446586768078</v>
       </c>
       <c r="D13">
-        <v>-0.11836969786330929</v>
+        <v>-0.1083141069980394</v>
       </c>
       <c r="E13">
-        <v>-0.1669216606030986</v>
+        <v>-0.1631794853789214</v>
       </c>
       <c r="F13">
-        <v>-0.1644161552848685</v>
+        <v>-0.1526732075581596</v>
       </c>
       <c r="G13">
-        <v>-2.419643871335718E-2</v>
+        <v>-0.008121960627003835</v>
       </c>
       <c r="H13">
-        <v>-1.348097452622686E-2</v>
+        <v>-0.004027723758629883</v>
       </c>
       <c r="I13">
-        <v>3.5424557054821011E-2</v>
+        <v>0.04656211036215085</v>
       </c>
       <c r="J13">
-        <v>0.1221648968582424</v>
+        <v>0.1196291661391423</v>
       </c>
       <c r="K13">
-        <v>0.19961791857552941</v>
+        <v>0.1998711389252365</v>
       </c>
       <c r="L13">
-        <v>0.21125592764987181</v>
+        <v>0.2088850523414891</v>
       </c>
       <c r="M13">
-        <v>0.2409125104829897</v>
+        <v>0.2319156624246561</v>
       </c>
       <c r="N13">
-        <v>0.24374816809592989</v>
+        <v>0.2378089985964852</v>
       </c>
       <c r="O13">
-        <v>0.26409705099696462</v>
+        <v>0.2551540197076285</v>
       </c>
       <c r="P13">
-        <v>0.2526028285032057</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.2482487881448249</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>-4.7260478410381217E-2</v>
+        <v>-0.04808359499714974</v>
       </c>
       <c r="C14">
-        <v>-6.9080870970323421E-2</v>
+        <v>-0.06989451551362991</v>
       </c>
       <c r="D14">
-        <v>-0.13387839415739131</v>
+        <v>-0.135959239701734</v>
       </c>
       <c r="E14">
-        <v>-0.14997455711509811</v>
+        <v>-0.1530254182300488</v>
       </c>
       <c r="F14">
-        <v>-0.20701425008281221</v>
+        <v>-0.218464555562508</v>
       </c>
       <c r="G14">
-        <v>-0.16436820059191129</v>
+        <v>-0.169145337263429</v>
       </c>
       <c r="H14">
-        <v>-5.1483531175584477E-2</v>
+        <v>-0.06452942683433709</v>
       </c>
       <c r="I14">
-        <v>3.1439369067921927E-2</v>
+        <v>0.02753580605314067</v>
       </c>
       <c r="J14">
-        <v>5.8723212801699752E-2</v>
+        <v>0.04629384918900507</v>
       </c>
       <c r="K14">
-        <v>8.2614726763016968E-2</v>
+        <v>0.07711068128583996</v>
       </c>
       <c r="L14">
-        <v>0.18634923619979921</v>
+        <v>0.1819680445369365</v>
       </c>
       <c r="M14">
-        <v>0.29965935389389758</v>
+        <v>0.2957630443815167</v>
       </c>
       <c r="N14">
-        <v>0.33603122980861422</v>
+        <v>0.3294373927558531</v>
       </c>
       <c r="O14">
-        <v>0.36860835258901392</v>
+        <v>0.3582996416016226</v>
       </c>
       <c r="P14">
-        <v>0.3889362015253367</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.3841058031065498</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>-4.9309270624202747E-2</v>
+        <v>-0.05173732756432053</v>
       </c>
       <c r="C15">
-        <v>-7.0643470091513366E-2</v>
+        <v>-0.07387379987922124</v>
       </c>
       <c r="D15">
-        <v>-0.13850308750901541</v>
+        <v>-0.1391800687413293</v>
       </c>
       <c r="E15">
-        <v>-0.15455959241612571</v>
+        <v>-0.1551677339159435</v>
       </c>
       <c r="F15">
-        <v>-0.21836079110459419</v>
+        <v>-0.2207788171001067</v>
       </c>
       <c r="G15">
-        <v>-0.17066763464796431</v>
+        <v>-0.1768674468017014</v>
       </c>
       <c r="H15">
-        <v>-6.569718238193975E-2</v>
+        <v>-0.06427439069833051</v>
       </c>
       <c r="I15">
-        <v>1.1798711355325141E-2</v>
+        <v>0.008967489720978114</v>
       </c>
       <c r="J15">
-        <v>4.4285584209138883E-2</v>
+        <v>0.0355495575624754</v>
       </c>
       <c r="K15">
-        <v>6.0696108073287659E-2</v>
+        <v>0.06604659091536197</v>
       </c>
       <c r="L15">
-        <v>0.15227660340106</v>
+        <v>0.1610332049896535</v>
       </c>
       <c r="M15">
-        <v>0.264410308071375</v>
+        <v>0.2635891532491328</v>
       </c>
       <c r="N15">
-        <v>0.3064465169451025</v>
+        <v>0.3041205993509052</v>
       </c>
       <c r="O15">
-        <v>0.33435213938056912</v>
+        <v>0.3269921843701484</v>
       </c>
       <c r="P15">
-        <v>0.35179175221539849</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3508115932889619</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>-4.4180028178068313E-2</v>
+        <v>-0.04446687221492021</v>
       </c>
       <c r="C16">
-        <v>-6.8196090293645484E-2</v>
+        <v>-0.06678599886700115</v>
       </c>
       <c r="D16">
-        <v>-0.13801290026490051</v>
+        <v>-0.133092069592516</v>
       </c>
       <c r="E16">
-        <v>-0.1615567531024196</v>
+        <v>-0.1482428139168927</v>
       </c>
       <c r="F16">
-        <v>-0.22503102446264089</v>
+        <v>-0.2061264177841818</v>
       </c>
       <c r="G16">
-        <v>-0.18478363064612291</v>
+        <v>-0.1730224609137091</v>
       </c>
       <c r="H16">
-        <v>-7.3911866773483006E-2</v>
+        <v>-0.0734038769405486</v>
       </c>
       <c r="I16">
-        <v>3.8604128923353169E-3</v>
+        <v>0.0166553908256215</v>
       </c>
       <c r="J16">
-        <v>3.1433431370948159E-2</v>
+        <v>0.0475133385834572</v>
       </c>
       <c r="K16">
-        <v>4.9001959963483971E-2</v>
+        <v>0.06818775118554771</v>
       </c>
       <c r="L16">
-        <v>0.1453340164903659</v>
+        <v>0.1548809851226439</v>
       </c>
       <c r="M16">
-        <v>0.25701418565967288</v>
+        <v>0.2613204978487133</v>
       </c>
       <c r="N16">
-        <v>0.29795866045498909</v>
+        <v>0.3093014510542076</v>
       </c>
       <c r="O16">
-        <v>0.33175410680130141</v>
+        <v>0.3427064481324353</v>
       </c>
       <c r="P16">
-        <v>0.362686909615199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.3609336804059985</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>-4.5047453440914369E-2</v>
+        <v>-0.04572540764015506</v>
       </c>
       <c r="C17">
-        <v>-6.9722566402566993E-2</v>
+        <v>-0.07038254004729758</v>
       </c>
       <c r="D17">
-        <v>-0.1356722088822489</v>
+        <v>-0.1386711192880916</v>
       </c>
       <c r="E17">
-        <v>-0.15870771930108021</v>
+        <v>-0.1568524062136908</v>
       </c>
       <c r="F17">
-        <v>-0.21740076895714411</v>
+        <v>-0.206877199238727</v>
       </c>
       <c r="G17">
-        <v>-0.1745937017232507</v>
+        <v>-0.1757930834748187</v>
       </c>
       <c r="H17">
-        <v>-7.1430158593434045E-2</v>
+        <v>-0.06828710596107077</v>
       </c>
       <c r="I17">
-        <v>9.4222813146103996E-3</v>
+        <v>0.02163875727083334</v>
       </c>
       <c r="J17">
-        <v>2.8009355503935341E-2</v>
+        <v>0.03663451699610781</v>
       </c>
       <c r="K17">
-        <v>4.2853457059292492E-2</v>
+        <v>0.05192965616571688</v>
       </c>
       <c r="L17">
-        <v>0.12601415553352641</v>
+        <v>0.1318304182993638</v>
       </c>
       <c r="M17">
-        <v>0.22775040402722871</v>
+        <v>0.2347247332788081</v>
       </c>
       <c r="N17">
-        <v>0.27410475231012499</v>
+        <v>0.2687167490995103</v>
       </c>
       <c r="O17">
-        <v>0.31103099943344659</v>
+        <v>0.3007002963299792</v>
       </c>
       <c r="P17">
-        <v>0.3324171682583198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.319515690843322</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-3.6279148859252951E-2</v>
+        <v>-0.03324441172796238</v>
       </c>
       <c r="C18">
-        <v>-0.1043702729633014</v>
+        <v>-0.1118730612158209</v>
       </c>
       <c r="D18">
-        <v>-6.5181386147707479E-2</v>
+        <v>-0.05671004413398258</v>
       </c>
       <c r="E18">
-        <v>-0.16054153016039799</v>
+        <v>-0.1638915953642507</v>
       </c>
       <c r="F18">
-        <v>5.0108040625402903E-2</v>
+        <v>0.06233836615829329</v>
       </c>
       <c r="G18">
-        <v>0.12893623707558829</v>
+        <v>0.1398011461922044</v>
       </c>
       <c r="H18">
-        <v>0.20995111048964021</v>
+        <v>0.216513369919801</v>
       </c>
       <c r="I18">
-        <v>0.30235447240247398</v>
+        <v>0.3064404133723341</v>
       </c>
       <c r="J18">
-        <v>0.36880955117911579</v>
+        <v>0.3702879597033081</v>
       </c>
       <c r="K18">
-        <v>0.39332297984938069</v>
+        <v>0.3896170179771431</v>
       </c>
       <c r="L18">
-        <v>0.41364594200421773</v>
+        <v>0.4150460230905172</v>
       </c>
       <c r="M18">
-        <v>0.41792141309023778</v>
+        <v>0.4233206098792783</v>
       </c>
       <c r="N18">
-        <v>0.3943355915638142</v>
+        <v>0.3950193390999827</v>
       </c>
       <c r="O18">
-        <v>0.37381074349288163</v>
+        <v>0.3724735410620446</v>
       </c>
       <c r="P18">
-        <v>0.35420526558947169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.3512037421869109</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>-3.92951202781908E-2</v>
+        <v>-0.03747800578326006</v>
       </c>
       <c r="C19">
-        <v>-0.13386230028897819</v>
+        <v>-0.1391249362925348</v>
       </c>
       <c r="D19">
-        <v>-9.5257639886315373E-2</v>
+        <v>-0.09751963475036297</v>
       </c>
       <c r="E19">
-        <v>-0.1336364143037225</v>
+        <v>-0.1485559962969978</v>
       </c>
       <c r="F19">
-        <v>0.1217983144532022</v>
+        <v>0.1110496794115079</v>
       </c>
       <c r="G19">
-        <v>0.20432215693660591</v>
+        <v>0.1955476426615595</v>
       </c>
       <c r="H19">
-        <v>0.27243368662779072</v>
+        <v>0.2696519303855587</v>
       </c>
       <c r="I19">
-        <v>0.35409804421814067</v>
+        <v>0.3502012457951503</v>
       </c>
       <c r="J19">
-        <v>0.40571205059819759</v>
+        <v>0.3964427780747922</v>
       </c>
       <c r="K19">
-        <v>0.41739849209921659</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0.43547316472074932</v>
+        <v>0.4092652347595571</v>
+      </c>
+      <c r="L19">
+        <v>0.4322564284528748</v>
       </c>
       <c r="M19">
-        <v>0.4344520760215585</v>
+        <v>0.4346961299285406</v>
       </c>
       <c r="N19">
-        <v>0.42067329836681761</v>
+        <v>0.4277818462249921</v>
       </c>
       <c r="O19">
-        <v>0.42731994585475119</v>
+        <v>0.4293157470341715</v>
       </c>
       <c r="P19">
-        <v>0.41831273275746378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4167370986831489</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>-3.9736733503420399E-2</v>
+        <v>-0.03691273779090792</v>
       </c>
       <c r="C20">
-        <v>-0.1581911490384024</v>
+        <v>-0.1470038550428452</v>
       </c>
       <c r="D20">
-        <v>-0.1074145062485726</v>
+        <v>-0.1084806214982054</v>
       </c>
       <c r="E20">
-        <v>-1.3897135843930739E-2</v>
+        <v>-0.01817334624716794</v>
       </c>
       <c r="F20">
-        <v>0.10403971837859061</v>
+        <v>0.09132960517714807</v>
       </c>
       <c r="G20">
-        <v>0.1404909144398658</v>
+        <v>0.1161355191973046</v>
       </c>
       <c r="H20">
-        <v>0.22783302823013471</v>
+        <v>0.213492732844479</v>
       </c>
       <c r="I20">
-        <v>0.30828812501052899</v>
+        <v>0.2985283521661848</v>
       </c>
       <c r="J20">
-        <v>0.34737149504696913</v>
+        <v>0.3401266851169133</v>
       </c>
       <c r="K20">
-        <v>0.39635751124165469</v>
+        <v>0.384463531495526</v>
       </c>
       <c r="L20">
-        <v>0.4022346557177352</v>
+        <v>0.3931755789314696</v>
       </c>
       <c r="M20">
-        <v>0.40828020008059968</v>
+        <v>0.3972897706299507</v>
       </c>
       <c r="N20">
-        <v>0.44875226909140958</v>
+        <v>0.4365706518777309</v>
       </c>
       <c r="O20">
-        <v>0.44889688061130079</v>
+        <v>0.4371537737006476</v>
       </c>
       <c r="P20">
-        <v>0.45232865942280248</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.4331722122125704</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>-2.528193344211379E-2</v>
+        <v>-0.02334707594584574</v>
       </c>
       <c r="C21">
-        <v>-0.1798906471635614</v>
+        <v>-0.1866885854365806</v>
       </c>
       <c r="D21">
-        <v>-0.1208881091653643</v>
+        <v>-0.1348516536432175</v>
       </c>
       <c r="E21">
-        <v>1.1936473502157209E-2</v>
+        <v>-0.01362758374560175</v>
       </c>
       <c r="F21">
-        <v>6.6082905042107634E-2</v>
+        <v>0.05189538556187615</v>
       </c>
       <c r="G21">
-        <v>9.0924739343405572E-2</v>
+        <v>0.08137399859106378</v>
       </c>
       <c r="H21">
-        <v>0.13748603591343811</v>
+        <v>0.1363534809165156</v>
       </c>
       <c r="I21">
-        <v>0.19625611065855991</v>
+        <v>0.1771938216111085</v>
       </c>
       <c r="J21">
-        <v>0.25524489005416379</v>
+        <v>0.2567529391222927</v>
       </c>
       <c r="K21">
-        <v>0.29773135853382537</v>
+        <v>0.2923893779586585</v>
       </c>
       <c r="L21">
-        <v>0.31244796459824592</v>
+        <v>0.3083295716797268</v>
       </c>
       <c r="M21">
-        <v>0.29444747517256359</v>
+        <v>0.2923539091645606</v>
       </c>
       <c r="N21">
-        <v>0.25472463996833422</v>
+        <v>0.2604942805217176</v>
       </c>
       <c r="O21">
-        <v>0.2309108300876927</v>
+        <v>0.2391474668012656</v>
       </c>
       <c r="P21">
-        <v>0.23862616430691941</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.2489051300180812</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>-1.9993350396702941E-2</v>
+        <v>-0.02325415210536802</v>
       </c>
       <c r="C22">
-        <v>-0.17802035979371841</v>
+        <v>-0.1831882922030569</v>
       </c>
       <c r="D22">
-        <v>-0.1160839278150176</v>
+        <v>-0.127459371179816</v>
       </c>
       <c r="E22">
-        <v>7.819029703144624E-3</v>
+        <v>0.007992810066180769</v>
       </c>
       <c r="F22">
-        <v>6.641817929175052E-2</v>
+        <v>0.06220966402277672</v>
       </c>
       <c r="G22">
-        <v>8.53433604053489E-2</v>
+        <v>0.0816210658440438</v>
       </c>
       <c r="H22">
-        <v>0.11379403543805271</v>
+        <v>0.1098006311829662</v>
       </c>
       <c r="I22">
-        <v>0.13931731223417701</v>
+        <v>0.1286881853650334</v>
       </c>
       <c r="J22">
-        <v>0.20780852273689759</v>
+        <v>0.1970431490551278</v>
       </c>
       <c r="K22">
-        <v>0.2544999005950937</v>
+        <v>0.2387557792789214</v>
       </c>
       <c r="L22">
-        <v>0.26306213267472639</v>
+        <v>0.2487954062366608</v>
       </c>
       <c r="M22">
-        <v>0.2687251086750771</v>
+        <v>0.2537606883678765</v>
       </c>
       <c r="N22">
-        <v>0.25209054207387249</v>
+        <v>0.2351152877833493</v>
       </c>
       <c r="O22">
-        <v>0.24686172376991589</v>
+        <v>0.2294834846096992</v>
       </c>
       <c r="P22">
-        <v>0.2455572417420617</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.2278860071787833</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>-3.7672906617533447E-2</v>
+        <v>-0.03326489323889399</v>
       </c>
       <c r="C23">
-        <v>-0.15070275789157189</v>
+        <v>-0.1474635156474074</v>
       </c>
       <c r="D23">
-        <v>-4.3319296616564182E-2</v>
+        <v>-0.02314808568866851</v>
       </c>
       <c r="E23">
-        <v>7.4190605262950252E-2</v>
+        <v>0.07485751941415114</v>
       </c>
       <c r="F23">
-        <v>0.21221165867025649</v>
+        <v>0.2188420234410349</v>
       </c>
       <c r="G23">
-        <v>0.30200190082923889</v>
+        <v>0.3077272637854153</v>
       </c>
       <c r="H23">
-        <v>0.33569530056918712</v>
+        <v>0.3399794976089098</v>
       </c>
       <c r="I23">
-        <v>0.35209973223644109</v>
+        <v>0.3571745328183165</v>
       </c>
       <c r="J23">
-        <v>0.37519391664180268</v>
+        <v>0.3749224052706703</v>
       </c>
       <c r="K23">
-        <v>0.37331336254577591</v>
+        <v>0.3690144964077461</v>
       </c>
       <c r="L23">
-        <v>0.36976911580233279</v>
+        <v>0.3623151035989185</v>
       </c>
       <c r="M23">
-        <v>0.35125474088296887</v>
+        <v>0.3464388218896167</v>
       </c>
       <c r="N23">
-        <v>0.34670892090184052</v>
+        <v>0.3404914154570606</v>
       </c>
       <c r="O23">
-        <v>0.34345042764668848</v>
+        <v>0.3365238836832425</v>
       </c>
       <c r="P23">
-        <v>0.32298965780249311</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.3188225708429545</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>-3.6831697838621731E-2</v>
+        <v>-0.0370486411866286</v>
       </c>
       <c r="C24">
-        <v>-1.977738763988521E-3</v>
+        <v>-0.002002338917554252</v>
       </c>
       <c r="D24">
-        <v>6.7328193743045162E-2</v>
+        <v>0.0593246667256266</v>
       </c>
       <c r="E24">
-        <v>-5.1587329493682768E-3</v>
+        <v>-0.01286902784468373</v>
       </c>
       <c r="F24">
-        <v>-2.3713032378160429E-2</v>
+        <v>-0.03004712281138446</v>
       </c>
       <c r="G24">
-        <v>-7.3343858300569678E-2</v>
+        <v>-0.08407976969448257</v>
       </c>
       <c r="H24">
-        <v>-6.3924529872929362E-2</v>
+        <v>-0.07419585036678883</v>
       </c>
       <c r="I24">
-        <v>-8.8277605463247533E-2</v>
+        <v>-0.1008812543978504</v>
       </c>
       <c r="J24">
-        <v>-0.16727614446915059</v>
+        <v>-0.178393088025166</v>
       </c>
       <c r="K24">
-        <v>-0.31355368442728537</v>
+        <v>-0.3247751908932399</v>
       </c>
       <c r="L24">
-        <v>-0.29541066390419218</v>
+        <v>-0.3172201425195671</v>
       </c>
       <c r="M24">
-        <v>-0.32934379419392279</v>
+        <v>-0.3514604612904817</v>
       </c>
       <c r="N24">
-        <v>-0.41640371045168278</v>
+        <v>-0.4465053461935007</v>
       </c>
       <c r="O24">
-        <v>-0.48913216883804611</v>
+        <v>-0.5200335447926415</v>
       </c>
       <c r="P24">
-        <v>-0.61346829069195419</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>-0.6291734173444817</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-0.16296477929297079</v>
+        <v>-0.1538840890504211</v>
       </c>
       <c r="C25">
-        <v>-0.1077293789094514</v>
+        <v>-0.09835657641436843</v>
       </c>
       <c r="D25">
-        <v>-0.1161549487621354</v>
+        <v>-0.108564905364894</v>
       </c>
       <c r="E25">
-        <v>-8.9402830379826714E-2</v>
+        <v>-0.08699783951237511</v>
       </c>
       <c r="F25">
-        <v>-0.15335170689076311</v>
+        <v>-0.140048370301564</v>
       </c>
       <c r="G25">
-        <v>-0.22620033524438971</v>
+        <v>-0.2098346658443764</v>
       </c>
       <c r="H25">
-        <v>-0.21913162798155281</v>
+        <v>-0.2100571360642921</v>
       </c>
       <c r="I25">
-        <v>-0.17402669327494541</v>
+        <v>-0.1694189313138173</v>
       </c>
       <c r="J25">
-        <v>-0.209480066815146</v>
+        <v>-0.211016939092021</v>
       </c>
       <c r="K25">
-        <v>-0.29750943591860268</v>
+        <v>-0.3059412987308206</v>
       </c>
       <c r="L25">
-        <v>-0.34772900038312232</v>
+        <v>-0.3597690442681866</v>
       </c>
       <c r="M25">
-        <v>-0.44096112655404029</v>
+        <v>-0.4557987830411551</v>
       </c>
       <c r="N25">
-        <v>-0.54817113110672833</v>
+        <v>-0.5670208490379525</v>
       </c>
       <c r="O25">
-        <v>-0.60357765291898635</v>
+        <v>-0.6198940909768101</v>
       </c>
       <c r="P25">
-        <v>-0.65339296273891045</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>-0.6587941394194393</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>-6.6017806270928736E-2</v>
+        <v>-0.06769430620935225</v>
       </c>
       <c r="C26">
-        <v>-3.4070467057786068E-2</v>
+        <v>-0.03155757069003649</v>
       </c>
       <c r="D26">
-        <v>4.904422253032014E-2</v>
+        <v>0.04522458476251937</v>
       </c>
       <c r="E26">
-        <v>6.9800388612603556E-2</v>
+        <v>0.06624728714623514</v>
       </c>
       <c r="F26">
-        <v>8.1858797611407116E-2</v>
+        <v>0.0795219230494283</v>
       </c>
       <c r="G26">
-        <v>0.1231731821023799</v>
+        <v>0.1146046092465791</v>
       </c>
       <c r="H26">
-        <v>0.13705105949086641</v>
+        <v>0.127984095746262</v>
       </c>
       <c r="I26">
-        <v>0.12921872735272791</v>
+        <v>0.1319066326383232</v>
       </c>
       <c r="J26">
-        <v>0.1696750717178703</v>
+        <v>0.1682671328457477</v>
       </c>
       <c r="K26">
-        <v>0.19313555224400769</v>
+        <v>0.200951297503126</v>
       </c>
       <c r="L26">
-        <v>0.1656172015882609</v>
+        <v>0.1704369540537203</v>
       </c>
       <c r="M26">
-        <v>0.18226815573272101</v>
+        <v>0.1894170947358043</v>
       </c>
       <c r="N26">
-        <v>0.16820099319870729</v>
+        <v>0.1624707189988563</v>
       </c>
       <c r="O26">
-        <v>0.13632345839176149</v>
+        <v>0.1391649537943931</v>
       </c>
       <c r="P26">
-        <v>0.1403409628649015</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.1390933831178851</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>-0.1227486311186186</v>
+        <v>-0.1177491306962131</v>
       </c>
       <c r="C27">
-        <v>-8.2472375577978929E-2</v>
+        <v>-0.07936111006377729</v>
       </c>
       <c r="D27">
-        <v>0.1125334396992396</v>
+        <v>0.1127821438566732</v>
       </c>
       <c r="E27">
-        <v>0.1374315790791785</v>
+        <v>0.123417757396492</v>
       </c>
       <c r="F27">
-        <v>0.1116236873669693</v>
+        <v>0.1095093909276492</v>
       </c>
       <c r="G27">
-        <v>0.1048887550463139</v>
+        <v>0.1031714104304308</v>
       </c>
       <c r="H27">
-        <v>9.599408355063363E-2</v>
+        <v>0.09469399050862776</v>
       </c>
       <c r="I27">
-        <v>4.4328890208824037E-2</v>
+        <v>0.05453247405299823</v>
       </c>
       <c r="J27">
-        <v>9.475104955657182E-2</v>
+        <v>0.100349875513952</v>
       </c>
       <c r="K27">
-        <v>0.1111794669214498</v>
+        <v>0.1131704319528543</v>
       </c>
       <c r="L27">
-        <v>0.1521810908055645</v>
+        <v>0.1453961880174355</v>
       </c>
       <c r="M27">
-        <v>0.18941304858551941</v>
+        <v>0.1852858585269195</v>
       </c>
       <c r="N27">
-        <v>0.18363533964052939</v>
+        <v>0.1845330164842662</v>
       </c>
       <c r="O27">
-        <v>0.15409137787262661</v>
+        <v>0.1556550667037256</v>
       </c>
       <c r="P27">
-        <v>0.12902673827620911</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.137946300435039</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>-6.4193757787664021E-2</v>
+        <v>-0.06329911698764076</v>
       </c>
       <c r="C28">
-        <v>-0.1142793243543852</v>
+        <v>-0.1172730905491431</v>
       </c>
       <c r="D28">
-        <v>-0.1747797419319817</v>
+        <v>-0.1726349806042995</v>
       </c>
       <c r="E28">
-        <v>-0.1315526780729516</v>
+        <v>-0.1323277613228747</v>
       </c>
       <c r="F28">
-        <v>-0.1100737019409799</v>
+        <v>-0.114476221805836</v>
       </c>
       <c r="G28">
-        <v>-5.9957153167284109E-2</v>
+        <v>-0.05941504249098294</v>
       </c>
       <c r="H28">
-        <v>-0.1133580121761662</v>
+        <v>-0.1111156245582142</v>
       </c>
       <c r="I28">
-        <v>-5.6274827195457858E-2</v>
+        <v>-0.05073479102647779</v>
       </c>
       <c r="J28">
-        <v>8.7385399424209087E-2</v>
+        <v>0.07661386684639469</v>
       </c>
       <c r="K28">
-        <v>0.19173610885980591</v>
+        <v>0.1949439467972967</v>
       </c>
       <c r="L28">
-        <v>0.2256213672136364</v>
+        <v>0.2283541557249358</v>
       </c>
       <c r="M28">
-        <v>0.20623083936054029</v>
+        <v>0.2024768790704259</v>
       </c>
       <c r="N28">
-        <v>0.14671834677436379</v>
+        <v>0.1449732336300049</v>
       </c>
       <c r="O28">
-        <v>8.4798421367701896E-2</v>
+        <v>0.08638835057250774</v>
       </c>
       <c r="P28">
-        <v>9.6283516506467885E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.003409890382122684</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-7.0566027251499991E-2</v>
+        <v>-0.07196788188040387</v>
       </c>
       <c r="C29">
-        <v>-0.128321906363907</v>
+        <v>-0.1263451147757606</v>
       </c>
       <c r="D29">
-        <v>-0.187467523979954</v>
+        <v>-0.1853313620109306</v>
       </c>
       <c r="E29">
-        <v>-0.1409685195862497</v>
+        <v>-0.1390069977771699</v>
       </c>
       <c r="F29">
-        <v>-0.1118703448065393</v>
+        <v>-0.1158826113618496</v>
       </c>
       <c r="G29">
-        <v>-9.3054427762764208E-2</v>
+        <v>-0.09576157281215598</v>
       </c>
       <c r="H29">
-        <v>-0.19476649291112061</v>
+        <v>-0.1871818630358159</v>
       </c>
       <c r="I29">
-        <v>-0.1412717104646623</v>
+        <v>-0.1177998441673866</v>
       </c>
       <c r="J29">
-        <v>-4.7154752033677187E-2</v>
+        <v>-0.0398165057973842</v>
       </c>
       <c r="K29">
-        <v>0.16787336368623651</v>
+        <v>0.163011923642781</v>
       </c>
       <c r="L29">
-        <v>0.1915715678090546</v>
+        <v>0.1946879863177405</v>
       </c>
       <c r="M29">
-        <v>0.2101452958737399</v>
+        <v>0.2148545580193736</v>
       </c>
       <c r="N29">
-        <v>0.18395283369554999</v>
+        <v>0.1884002797957192</v>
       </c>
       <c r="O29">
-        <v>0.13117483681597281</v>
+        <v>0.1367678550590751</v>
       </c>
       <c r="P29">
-        <v>6.1812471777467647E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.0720583866840119</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-7.0960003442138431E-2</v>
+        <v>-0.06820513997892169</v>
       </c>
       <c r="C30">
-        <v>-0.13470250532306791</v>
+        <v>-0.1284330252703835</v>
       </c>
       <c r="D30">
-        <v>-0.15320408624080531</v>
+        <v>-0.1413239421058464</v>
       </c>
       <c r="E30">
-        <v>-9.0098246232145046E-2</v>
+        <v>-0.08127428697157131</v>
       </c>
       <c r="F30">
-        <v>-0.1247819526361157</v>
+        <v>-0.1285553506051062</v>
       </c>
       <c r="G30">
-        <v>-9.3529994961356389E-2</v>
+        <v>-0.09174131883287052</v>
       </c>
       <c r="H30">
-        <v>2.0146538871210429E-2</v>
+        <v>0.008786651344780299</v>
       </c>
       <c r="I30">
-        <v>-4.7150233663515791E-2</v>
+        <v>-0.05189460781608334</v>
       </c>
       <c r="J30">
-        <v>9.5807683533263507E-2</v>
+        <v>0.08542049197444349</v>
       </c>
       <c r="K30">
-        <v>0.1769614931719842</v>
+        <v>0.1746613578725859</v>
       </c>
       <c r="L30">
-        <v>0.18492068449423629</v>
+        <v>0.1920376319685743</v>
       </c>
       <c r="M30">
-        <v>0.1582572895065745</v>
+        <v>0.172775812508089</v>
       </c>
       <c r="N30">
-        <v>0.1171157669017653</v>
+        <v>0.1366976301183994</v>
       </c>
       <c r="O30">
-        <v>5.668510147047965E-2</v>
+        <v>0.07136848068773059</v>
       </c>
       <c r="P30">
-        <v>-2.7962891027846701E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>-0.01427525921144917</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>-6.6943979105147308E-2</v>
+        <v>-0.0687066357074681</v>
       </c>
       <c r="C31">
-        <v>-0.12917984778318009</v>
+        <v>-0.135707065632097</v>
       </c>
       <c r="D31">
-        <v>-0.14152279544608351</v>
+        <v>-0.1502166609367696</v>
       </c>
       <c r="E31">
-        <v>-8.9071282691239317E-2</v>
+        <v>-0.09180169800958521</v>
       </c>
       <c r="F31">
-        <v>-0.1198720360685811</v>
+        <v>-0.1263864416903532</v>
       </c>
       <c r="G31">
-        <v>-9.3927284499356153E-2</v>
+        <v>-0.09989851253912074</v>
       </c>
       <c r="H31">
-        <v>1.8685871062892781E-3</v>
+        <v>0.001074478903998269</v>
       </c>
       <c r="I31">
-        <v>-4.9453726930440103E-2</v>
+        <v>-0.07005202890519824</v>
       </c>
       <c r="J31">
-        <v>5.9255760211279693E-2</v>
+        <v>0.0534211817714293</v>
       </c>
       <c r="K31">
-        <v>0.1859059067638163</v>
+        <v>0.1904718640678876</v>
       </c>
       <c r="L31">
-        <v>0.2445614542222477</v>
+        <v>0.2506366605116656</v>
       </c>
       <c r="M31">
-        <v>0.27747132828314169</v>
+        <v>0.2857865796363692</v>
       </c>
       <c r="N31">
-        <v>0.29231791412771468</v>
+        <v>0.3004243207230871</v>
       </c>
       <c r="O31">
-        <v>0.2548650083977762</v>
+        <v>0.2713710449747959</v>
       </c>
       <c r="P31">
-        <v>0.24913958836643971</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.2672551840714792</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>-6.9451356677875914E-2</v>
+        <v>-0.06859594505090771</v>
       </c>
       <c r="C32">
-        <v>-0.13000891147669361</v>
+        <v>-0.1213314881623955</v>
       </c>
       <c r="D32">
-        <v>-0.18070252278273469</v>
+        <v>-0.1771534559419858</v>
       </c>
       <c r="E32">
-        <v>-0.14084968285144259</v>
+        <v>-0.1318607279293235</v>
       </c>
       <c r="F32">
-        <v>-0.11583737111977239</v>
+        <v>-0.112314809775858</v>
       </c>
       <c r="G32">
-        <v>-9.8170591575890254E-2</v>
+        <v>-0.09721119758310341</v>
       </c>
       <c r="H32">
-        <v>-0.1624105210467407</v>
+        <v>-0.1641335290817526</v>
       </c>
       <c r="I32">
-        <v>-0.1319944457044594</v>
+        <v>-0.1334759373032734</v>
       </c>
       <c r="J32">
-        <v>-6.3273965551636044E-2</v>
+        <v>-0.06980341848804239</v>
       </c>
       <c r="K32">
-        <v>0.14028205156821999</v>
+        <v>0.1347600666480338</v>
       </c>
       <c r="L32">
-        <v>0.19161176384689549</v>
+        <v>0.1934858914475964</v>
       </c>
       <c r="M32">
-        <v>0.22010570528011539</v>
+        <v>0.222730969920941</v>
       </c>
       <c r="N32">
-        <v>0.22940561780762389</v>
+        <v>0.243882766536665</v>
       </c>
       <c r="O32">
-        <v>0.2348336524005146</v>
+        <v>0.2423485232288732</v>
       </c>
       <c r="P32">
-        <v>0.2270812567517024</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.2439521585617673</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>-7.1624819907712273E-2</v>
+        <v>-0.07036897738487652</v>
       </c>
       <c r="C33">
-        <v>-0.13001798231796599</v>
+        <v>-0.1263309138545374</v>
       </c>
       <c r="D33">
-        <v>-0.1854856365931779</v>
+        <v>-0.1805692241981732</v>
       </c>
       <c r="E33">
-        <v>-0.13989067353051521</v>
+        <v>-0.1355897630033474</v>
       </c>
       <c r="F33">
-        <v>-0.1150823700922389</v>
+        <v>-0.1140028018707256</v>
       </c>
       <c r="G33">
-        <v>-9.5637678183928612E-2</v>
+        <v>-0.08853019301788768</v>
       </c>
       <c r="H33">
-        <v>-0.16845687580384949</v>
+        <v>-0.1524610618094581</v>
       </c>
       <c r="I33">
-        <v>-0.12926732731360949</v>
+        <v>-0.1174742260544562</v>
       </c>
       <c r="J33">
-        <v>-6.5483075439715877E-2</v>
+        <v>-0.05695712387994504</v>
       </c>
       <c r="K33">
-        <v>0.1455131951688961</v>
+        <v>0.156910461047403</v>
       </c>
       <c r="L33">
-        <v>0.20202919746818371</v>
+        <v>0.2081470236714941</v>
       </c>
       <c r="M33">
-        <v>0.24210279355804881</v>
+        <v>0.2400377928718302</v>
       </c>
       <c r="N33">
-        <v>0.25740335675730958</v>
+        <v>0.2616902778732571</v>
       </c>
       <c r="O33">
-        <v>0.27026270305988848</v>
+        <v>0.2735577487026971</v>
       </c>
       <c r="P33">
-        <v>0.270620945966353</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.2797437532114336</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>-6.8393092279329146E-2</v>
+        <v>-0.06477972953569178</v>
       </c>
       <c r="C34">
-        <v>-0.12583608535029511</v>
+        <v>-0.1202359181252856</v>
       </c>
       <c r="D34">
-        <v>-0.17915998749021789</v>
+        <v>-0.1780635537894117</v>
       </c>
       <c r="E34">
-        <v>-0.13664028421020971</v>
+        <v>-0.136086799783359</v>
       </c>
       <c r="F34">
-        <v>-0.1200173298150662</v>
+        <v>-0.1086013436232022</v>
       </c>
       <c r="G34">
-        <v>-9.6352942944846531E-2</v>
+        <v>-0.0868998561928853</v>
       </c>
       <c r="H34">
-        <v>-0.16148532328059209</v>
+        <v>-0.1542448600861834</v>
       </c>
       <c r="I34">
-        <v>-0.1312292978633845</v>
+        <v>-0.1295109162250175</v>
       </c>
       <c r="J34">
-        <v>-7.0901033245555009E-2</v>
+        <v>-0.07298023806954747</v>
       </c>
       <c r="K34">
-        <v>0.13666012792076351</v>
+        <v>0.1322908915018153</v>
       </c>
       <c r="L34">
-        <v>0.18990586484813679</v>
+        <v>0.1913387604796715</v>
       </c>
       <c r="M34">
-        <v>0.2337881023972517</v>
+        <v>0.2277903447694547</v>
       </c>
       <c r="N34">
-        <v>0.24560837999685481</v>
+        <v>0.2442521896184236</v>
       </c>
       <c r="O34">
-        <v>0.2602489427173979</v>
+        <v>0.2603460709151708</v>
       </c>
       <c r="P34">
-        <v>0.26201172359648051</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2672428206104651</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>-7.570768710207075E-2</v>
+        <v>-0.06790359372289741</v>
       </c>
       <c r="C35">
-        <v>-0.13532723966104199</v>
+        <v>-0.1273036036303488</v>
       </c>
       <c r="D35">
-        <v>-0.18971189898011409</v>
+        <v>-0.1834179561283044</v>
       </c>
       <c r="E35">
-        <v>-0.14774646051098969</v>
+        <v>-0.1408448801758455</v>
       </c>
       <c r="F35">
-        <v>-0.12818335186774019</v>
+        <v>-0.1201896392944321</v>
       </c>
       <c r="G35">
-        <v>-0.1028371381882409</v>
+        <v>-0.1013665555359215</v>
       </c>
       <c r="H35">
-        <v>-0.17052329671289179</v>
+        <v>-0.1701584875691323</v>
       </c>
       <c r="I35">
-        <v>-0.1461913928024442</v>
+        <v>-0.1526963503378757</v>
       </c>
       <c r="J35">
-        <v>-0.10132705528196061</v>
+        <v>-0.1028148443600771</v>
       </c>
       <c r="K35">
-        <v>0.10124370229214021</v>
+        <v>0.09212965610655245</v>
       </c>
       <c r="L35">
-        <v>0.1631645523596984</v>
+        <v>0.1599783713314957</v>
       </c>
       <c r="M35">
-        <v>0.20069134920471321</v>
+        <v>0.1984236331966802</v>
       </c>
       <c r="N35">
-        <v>0.2336729647799469</v>
+        <v>0.2325993538599243</v>
       </c>
       <c r="O35">
-        <v>0.25012575180953539</v>
+        <v>0.2462679976127067</v>
       </c>
       <c r="P35">
-        <v>0.27272202223688469</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.2724713821490902</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>-6.8087595132014622E-2</v>
+        <v>-0.0721339185114406</v>
       </c>
       <c r="C36">
-        <v>-0.12516826502023429</v>
+        <v>-0.1351381094511153</v>
       </c>
       <c r="D36">
-        <v>-0.17964018380828101</v>
+        <v>-0.1861796798324897</v>
       </c>
       <c r="E36">
-        <v>-0.1384081933804886</v>
+        <v>-0.1380635306930806</v>
       </c>
       <c r="F36">
-        <v>-0.1121504735208963</v>
+        <v>-0.1213255157727141</v>
       </c>
       <c r="G36">
-        <v>-9.7075878554941597E-2</v>
+        <v>-0.1031196871506868</v>
       </c>
       <c r="H36">
-        <v>-0.1649365745331704</v>
+        <v>-0.1816512023480472</v>
       </c>
       <c r="I36">
-        <v>-0.12686782819532491</v>
+        <v>-0.133657869941571</v>
       </c>
       <c r="J36">
-        <v>-5.7280217657977292E-2</v>
+        <v>-0.06871182882532234</v>
       </c>
       <c r="K36">
-        <v>0.15204155934166691</v>
+        <v>0.1525699599214737</v>
       </c>
       <c r="L36">
-        <v>0.20329501634480621</v>
+        <v>0.2001574959473308</v>
       </c>
       <c r="M36">
-        <v>0.2291239811085935</v>
+        <v>0.2393891922822456</v>
       </c>
       <c r="N36">
-        <v>0.24063541408280309</v>
+        <v>0.2476648774921084</v>
       </c>
       <c r="O36">
-        <v>0.23304928797309149</v>
+        <v>0.2357844166244319</v>
       </c>
       <c r="P36">
-        <v>0.21313791105271629</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.2179801808868344</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>-6.432889901847641E-2</v>
+        <v>-0.06454228510022104</v>
       </c>
       <c r="C37">
-        <v>-0.1198064908807423</v>
+        <v>-0.1170581244658114</v>
       </c>
       <c r="D37">
-        <v>-0.17331116508186781</v>
+        <v>-0.168523030763478</v>
       </c>
       <c r="E37">
-        <v>-0.1325330126761772</v>
+        <v>-0.1286991140679776</v>
       </c>
       <c r="F37">
-        <v>-0.11103737853538009</v>
+        <v>-0.1026973343568724</v>
       </c>
       <c r="G37">
-        <v>-8.795197516967318E-2</v>
+        <v>-0.08700583672619648</v>
       </c>
       <c r="H37">
-        <v>-0.16213467301851919</v>
+        <v>-0.1526654126139093</v>
       </c>
       <c r="I37">
-        <v>-0.1277987750126702</v>
+        <v>-0.1210936745463852</v>
       </c>
       <c r="J37">
-        <v>-6.1453400836442691E-2</v>
+        <v>-0.0602744065687502</v>
       </c>
       <c r="K37">
-        <v>0.15294058068691421</v>
+        <v>0.1549736812785982</v>
       </c>
       <c r="L37">
-        <v>0.1984730131561083</v>
+        <v>0.2009921909146428</v>
       </c>
       <c r="M37">
-        <v>0.23593348536498299</v>
+        <v>0.2350732631338469</v>
       </c>
       <c r="N37">
-        <v>0.23665729605231009</v>
+        <v>0.2383605441085981</v>
       </c>
       <c r="O37">
-        <v>0.23388758731191089</v>
+        <v>0.2339551979577682</v>
       </c>
       <c r="P37">
-        <v>0.2135560043498799</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.2150009197595915</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>-7.1230244122222425E-2</v>
+        <v>-0.06840291074110766</v>
       </c>
       <c r="C38">
-        <v>-0.1305216892122178</v>
+        <v>-0.1240253908900542</v>
       </c>
       <c r="D38">
-        <v>-0.18847825651922279</v>
+        <v>-0.1757527072770098</v>
       </c>
       <c r="E38">
-        <v>-0.13937828778013439</v>
+        <v>-0.1260678251495131</v>
       </c>
       <c r="F38">
-        <v>-0.11752456680644011</v>
+        <v>-0.1042532588916723</v>
       </c>
       <c r="G38">
-        <v>-9.5063146909712154E-2</v>
+        <v>-0.08192876986831368</v>
       </c>
       <c r="H38">
-        <v>-0.16251781110186861</v>
+        <v>-0.1414770221243415</v>
       </c>
       <c r="I38">
-        <v>-0.12147986450931759</v>
+        <v>-0.1153480303952312</v>
       </c>
       <c r="J38">
-        <v>-6.2002880591622157E-2</v>
+        <v>-0.05413327439363098</v>
       </c>
       <c r="K38">
-        <v>0.1450801043090226</v>
+        <v>0.1506842528625266</v>
       </c>
       <c r="L38">
-        <v>0.1954244657105137</v>
+        <v>0.1989662170504575</v>
       </c>
       <c r="M38">
-        <v>0.23025766252940341</v>
+        <v>0.2298094633009644</v>
       </c>
       <c r="N38">
-        <v>0.2350067747569119</v>
+        <v>0.2416132513100508</v>
       </c>
       <c r="O38">
-        <v>0.23278355637203149</v>
+        <v>0.2509670477103361</v>
       </c>
       <c r="P38">
-        <v>0.22353074322807071</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.2307279913714483</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>-6.8946452711157569E-2</v>
+        <v>-0.07056549107845414</v>
       </c>
       <c r="C39">
-        <v>-0.12828433486688659</v>
+        <v>-0.1285210767342237</v>
       </c>
       <c r="D39">
-        <v>-0.18670479872381579</v>
+        <v>-0.1809159051540843</v>
       </c>
       <c r="E39">
-        <v>-0.1418063350337668</v>
+        <v>-0.1384791670646802</v>
       </c>
       <c r="F39">
-        <v>-0.12224120934745381</v>
+        <v>-0.1113555858077294</v>
       </c>
       <c r="G39">
-        <v>-9.8971349528883146E-2</v>
+        <v>-0.09427409692311646</v>
       </c>
       <c r="H39">
-        <v>-0.17154079172193881</v>
+        <v>-0.1604388020159296</v>
       </c>
       <c r="I39">
-        <v>-0.13641214006510691</v>
+        <v>-0.1280778490391066</v>
       </c>
       <c r="J39">
-        <v>-8.1565702135141152E-2</v>
+        <v>-0.06580792466901621</v>
       </c>
       <c r="K39">
-        <v>0.12246512887992179</v>
+        <v>0.1405305281617079</v>
       </c>
       <c r="L39">
-        <v>0.17698384262263189</v>
+        <v>0.1864114933886937</v>
       </c>
       <c r="M39">
-        <v>0.2090233361520302</v>
+        <v>0.2232575210656444</v>
       </c>
       <c r="N39">
-        <v>0.22784817266197649</v>
+        <v>0.2334214865097468</v>
       </c>
       <c r="O39">
-        <v>0.23332222268112279</v>
+        <v>0.238274921913969</v>
       </c>
       <c r="P39">
-        <v>0.22757194244816331</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.2251361479085532</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>-6.8737313517325663E-2</v>
+        <v>-0.0700839122959018</v>
       </c>
       <c r="C40">
-        <v>-0.129843131671144</v>
+        <v>-0.1246390809867833</v>
       </c>
       <c r="D40">
-        <v>-0.1850821557342657</v>
+        <v>-0.1746652881136436</v>
       </c>
       <c r="E40">
-        <v>-0.13976281014843051</v>
+        <v>-0.1315818480630474</v>
       </c>
       <c r="F40">
-        <v>-0.11619684116887589</v>
+        <v>-0.1114689274671426</v>
       </c>
       <c r="G40">
-        <v>-9.1054973510052289E-2</v>
+        <v>-0.0915712203027407</v>
       </c>
       <c r="H40">
-        <v>-0.145388153504071</v>
+        <v>-0.1539180825266185</v>
       </c>
       <c r="I40">
-        <v>-0.12285154607780201</v>
+        <v>-0.1265828903320221</v>
       </c>
       <c r="J40">
-        <v>-7.1702984664485228E-2</v>
+        <v>-0.07101044696594994</v>
       </c>
       <c r="K40">
-        <v>0.10987684386996791</v>
+        <v>0.1193249762433049</v>
       </c>
       <c r="L40">
-        <v>0.17332256069754931</v>
+        <v>0.180693923533164</v>
       </c>
       <c r="M40">
-        <v>0.1947646833872958</v>
+        <v>0.2126597009920081</v>
       </c>
       <c r="N40">
-        <v>0.22688156641765331</v>
+        <v>0.2443278447232468</v>
       </c>
       <c r="O40">
-        <v>0.24705434416493049</v>
+        <v>0.2574297301517036</v>
       </c>
       <c r="P40">
-        <v>0.27194453511508287</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.2853069982783915</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>-0.1118446996679827</v>
+        <v>-0.1127519278908456</v>
       </c>
       <c r="C41">
-        <v>-0.17314468594967661</v>
+        <v>-0.1845773529806243</v>
       </c>
       <c r="D41">
-        <v>-0.10437392128103611</v>
+        <v>-0.1184118162536125</v>
       </c>
       <c r="E41">
-        <v>-2.6630047396081571E-2</v>
+        <v>-0.03027874800478106</v>
       </c>
       <c r="F41">
-        <v>-8.4583209575569251E-2</v>
+        <v>-0.09083468429934188</v>
       </c>
       <c r="G41">
-        <v>-3.1532002108426938E-2</v>
+        <v>-0.03910743668687493</v>
       </c>
       <c r="H41">
-        <v>7.1826565650381563E-2</v>
+        <v>0.05673137510353977</v>
       </c>
       <c r="I41">
-        <v>0.1042207110481712</v>
+        <v>0.09344685230918122</v>
       </c>
       <c r="J41">
-        <v>9.3007234065256794E-2</v>
+        <v>0.08805539735379704</v>
       </c>
       <c r="K41">
-        <v>9.0541193106579029E-2</v>
+        <v>0.09597523839040585</v>
       </c>
       <c r="L41">
-        <v>7.7627622998689735E-2</v>
+        <v>0.07856245089623948</v>
       </c>
       <c r="M41">
-        <v>2.9656072205948389E-2</v>
+        <v>0.03635912311581361</v>
       </c>
       <c r="N41">
-        <v>5.450396119065902E-2</v>
+        <v>0.05804176653358017</v>
       </c>
       <c r="O41">
-        <v>5.4331565102264327E-2</v>
+        <v>0.06104655999312922</v>
       </c>
       <c r="P41">
-        <v>5.229321688222819E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.06051774178650015</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>-8.6920123148567424E-2</v>
+        <v>-0.08440044907419662</v>
       </c>
       <c r="C42">
-        <v>-0.1751479308656497</v>
+        <v>-0.1675190824107607</v>
       </c>
       <c r="D42">
-        <v>-0.14769080995625861</v>
+        <v>-0.1398854879172393</v>
       </c>
       <c r="E42">
-        <v>-5.207043851039859E-3</v>
+        <v>0.006924536900875451</v>
       </c>
       <c r="F42">
-        <v>1.9380545287887671E-2</v>
+        <v>0.02751265382431366</v>
       </c>
       <c r="G42">
-        <v>0.1504921092983133</v>
+        <v>0.1520614114160024</v>
       </c>
       <c r="H42">
-        <v>0.28303291832374883</v>
+        <v>0.2694625255723069</v>
       </c>
       <c r="I42">
-        <v>0.27351254987234469</v>
+        <v>0.2674576804399398</v>
       </c>
       <c r="J42">
-        <v>0.2305036496478923</v>
+        <v>0.2262830983381857</v>
       </c>
       <c r="K42">
-        <v>0.18896570840487081</v>
+        <v>0.182329053233986</v>
       </c>
       <c r="L42">
-        <v>0.1873446062546166</v>
+        <v>0.1772643719741784</v>
       </c>
       <c r="M42">
-        <v>0.17114875644895999</v>
+        <v>0.1641928142385302</v>
       </c>
       <c r="N42">
-        <v>0.1882722114932362</v>
+        <v>0.1722982993747067</v>
       </c>
       <c r="O42">
-        <v>0.20548309661747771</v>
+        <v>0.1913391762330252</v>
       </c>
       <c r="P42">
-        <v>0.214695415464423</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.20324972746184</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>-8.1965358069684288E-2</v>
+        <v>-0.08597604976404592</v>
       </c>
       <c r="C43">
-        <v>-0.15676765135220261</v>
+        <v>-0.1546324534342997</v>
       </c>
       <c r="D43">
-        <v>-0.11980960874688509</v>
+        <v>-0.1149410956345631</v>
       </c>
       <c r="E43">
-        <v>5.5742026946287524E-3</v>
+        <v>-0.0008803011178761527</v>
       </c>
       <c r="F43">
-        <v>1.106521051228071E-2</v>
+        <v>0.009961905302081879</v>
       </c>
       <c r="G43">
-        <v>0.11437791809484139</v>
+        <v>0.1131506245529324</v>
       </c>
       <c r="H43">
-        <v>0.24630952414686719</v>
+        <v>0.2462991809072787</v>
       </c>
       <c r="I43">
-        <v>0.23778849038360811</v>
+        <v>0.2382626887641738</v>
       </c>
       <c r="J43">
-        <v>0.24980537117541959</v>
+        <v>0.2452430414473567</v>
       </c>
       <c r="K43">
-        <v>0.24660276435767969</v>
+        <v>0.2361838302333045</v>
       </c>
       <c r="L43">
-        <v>0.2264833459961092</v>
+        <v>0.2284034506572805</v>
       </c>
       <c r="M43">
-        <v>0.25101964973406782</v>
+        <v>0.2445248373235853</v>
       </c>
       <c r="N43">
-        <v>0.23247145322767551</v>
+        <v>0.2331139510721608</v>
       </c>
       <c r="O43">
-        <v>0.21425827609959461</v>
+        <v>0.2150877334648114</v>
       </c>
       <c r="P43">
-        <v>0.21093991723883579</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
+        <v>0.2208504471999506</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B44">
-        <v>-0.114355928774692</v>
+        <v>-0.1166150191957295</v>
       </c>
       <c r="C44">
-        <v>-8.1198481301916481E-2</v>
+        <v>-0.08568569649923764</v>
       </c>
       <c r="D44">
-        <v>5.9036140510249739E-3</v>
+        <v>0.004241334884028243</v>
       </c>
       <c r="E44">
-        <v>-2.593187529632672E-2</v>
+        <v>-0.02672946074656913</v>
       </c>
       <c r="F44">
-        <v>9.8388051525612724E-2</v>
+        <v>0.09349631760754622</v>
       </c>
       <c r="G44">
-        <v>0.14698683615652999</v>
+        <v>0.1589402298102577</v>
       </c>
       <c r="H44">
-        <v>0.15322012786844719</v>
+        <v>0.1531402466899255</v>
       </c>
       <c r="I44">
-        <v>0.1165761668661473</v>
+        <v>0.1142779581220504</v>
       </c>
       <c r="J44">
-        <v>0.1080208740698068</v>
+        <v>0.1091444274164672</v>
       </c>
       <c r="K44">
-        <v>0.14705551020031471</v>
+        <v>0.1454036879137125</v>
       </c>
       <c r="L44">
-        <v>0.13790216490475279</v>
+        <v>0.1345505032154249</v>
       </c>
       <c r="M44">
-        <v>0.15322792511473979</v>
+        <v>0.149137520801843</v>
       </c>
       <c r="N44">
-        <v>0.1319048673506176</v>
+        <v>0.1305526886593854</v>
       </c>
       <c r="O44">
-        <v>9.8848986057551214E-2</v>
+        <v>0.1014556306136796</v>
       </c>
       <c r="P44">
-        <v>3.7298390643859848E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
+        <v>0.04702939450096722</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B45">
-        <v>-0.1145505910409978</v>
+        <v>-0.116874542353285</v>
       </c>
       <c r="C45">
-        <v>-0.27389672700727702</v>
+        <v>-0.2878704572774626</v>
       </c>
       <c r="D45">
-        <v>-0.17940292150905421</v>
+        <v>-0.187799904839801</v>
       </c>
       <c r="E45">
-        <v>-0.1839133322604421</v>
+        <v>-0.1827139760012107</v>
       </c>
       <c r="F45">
-        <v>-0.1068309625778677</v>
+        <v>-0.1094907254695902</v>
       </c>
       <c r="G45">
-        <v>-8.6337081547349592E-2</v>
+        <v>-0.08701596080538532</v>
       </c>
       <c r="H45">
-        <v>-6.4081798394514791E-2</v>
+        <v>-0.06740292888462757</v>
       </c>
       <c r="I45">
-        <v>-1.8331532217204419E-2</v>
+        <v>-0.02205119611961466</v>
       </c>
       <c r="J45">
-        <v>-5.2342140001116512E-2</v>
+        <v>-0.04786607318354285</v>
       </c>
       <c r="K45">
-        <v>-7.9856798446708788E-2</v>
+        <v>-0.08034205116146179</v>
       </c>
       <c r="L45">
-        <v>-8.7360068651246153E-2</v>
+        <v>-0.07656221969087956</v>
       </c>
       <c r="M45">
-        <v>-0.106224257334019</v>
+        <v>-0.09775330883981487</v>
       </c>
       <c r="N45">
-        <v>-0.1599270010312264</v>
+        <v>-0.1516917517577817</v>
       </c>
       <c r="O45">
-        <v>-0.16698744795298401</v>
+        <v>-0.1604993568501384</v>
       </c>
       <c r="P45">
-        <v>-0.1811121804644053</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
+        <v>-0.1807044947349789</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B46">
-        <v>-1.861109764116263E-2</v>
+        <v>-0.01943771833120425</v>
       </c>
       <c r="C46">
-        <v>-0.29658702280945592</v>
+        <v>-0.2994513016716448</v>
       </c>
       <c r="D46">
-        <v>-0.1614874939887849</v>
+        <v>-0.1637327707003554</v>
       </c>
       <c r="E46">
-        <v>5.6416766998787428E-2</v>
+        <v>0.06748415787772544</v>
       </c>
       <c r="F46">
-        <v>0.12510389259787419</v>
+        <v>0.1315146608101443</v>
       </c>
       <c r="G46">
-        <v>0.18087146742805771</v>
+        <v>0.1766658110622349</v>
       </c>
       <c r="H46">
-        <v>0.25916671182619411</v>
+        <v>0.2610426336871491</v>
       </c>
       <c r="I46">
-        <v>0.26443071739843083</v>
+        <v>0.2687420795085386</v>
       </c>
       <c r="J46">
-        <v>0.25586608524368509</v>
+        <v>0.2531381398036315</v>
       </c>
       <c r="K46">
-        <v>0.28182561817991347</v>
+        <v>0.274631149011539</v>
       </c>
       <c r="L46">
-        <v>0.27927574570004088</v>
+        <v>0.2689749068005968</v>
       </c>
       <c r="M46">
-        <v>0.25875808761239438</v>
+        <v>0.2480267432609486</v>
       </c>
       <c r="N46">
-        <v>0.25568669586002962</v>
+        <v>0.2435731624676962</v>
       </c>
       <c r="O46">
-        <v>0.2534208805850397</v>
+        <v>0.2436665003420025</v>
       </c>
       <c r="P46">
-        <v>0.23787187828625289</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
+        <v>0.2261691810490172</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B47">
-        <v>-6.6809958973357939E-2</v>
+        <v>-0.07951112901220368</v>
       </c>
       <c r="C47">
-        <v>-0.1111874509763435</v>
+        <v>-0.1261401422125007</v>
       </c>
       <c r="D47">
-        <v>-1.5976295228262188E-2</v>
+        <v>-0.02653928998160525</v>
       </c>
       <c r="E47">
-        <v>2.2687743368239172E-2</v>
+        <v>0.005104004100516939</v>
       </c>
       <c r="F47">
-        <v>0.17224138686794049</v>
+        <v>0.1722873209920883</v>
       </c>
       <c r="G47">
-        <v>0.22809434415314031</v>
+        <v>0.2197105970503698</v>
       </c>
       <c r="H47">
-        <v>0.25927647342325089</v>
+        <v>0.2591090234908717</v>
       </c>
       <c r="I47">
-        <v>0.25406266323812332</v>
+        <v>0.2463352691423424</v>
       </c>
       <c r="J47">
-        <v>0.22012616070430541</v>
+        <v>0.2146271440582258</v>
       </c>
       <c r="K47">
-        <v>0.25302957139816978</v>
+        <v>0.2483973378590129</v>
       </c>
       <c r="L47">
-        <v>0.2589823243594232</v>
+        <v>0.2491990064580432</v>
       </c>
       <c r="M47">
-        <v>0.26198322426754711</v>
+        <v>0.2495246518748517</v>
       </c>
       <c r="N47">
-        <v>0.24112050233856669</v>
+        <v>0.2274615478490895</v>
       </c>
       <c r="O47">
-        <v>0.22123429960620369</v>
+        <v>0.2108466063230615</v>
       </c>
       <c r="P47">
-        <v>0.20136344676165821</v>
+        <v>0.1858888790251589</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P19 B21:P47 B20:O20">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/ratio.alpha.natif/Resultats_ratio.alpha.natif_moy_ADJR2.xlsx
@@ -1,21 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.alpha.natif\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV0_ADJR2</t>
+  </si>
+  <si>
+    <t>LV1_ADJR2</t>
+  </si>
+  <si>
+    <t>LV2_ADJR2</t>
+  </si>
+  <si>
+    <t>LV3_ADJR2</t>
+  </si>
+  <si>
+    <t>LV4_ADJR2</t>
+  </si>
+  <si>
+    <t>LV5_ADJR2</t>
+  </si>
+  <si>
+    <t>LV6_ADJR2</t>
+  </si>
+  <si>
+    <t>LV7_ADJR2</t>
+  </si>
+  <si>
+    <t>LV8_ADJR2</t>
+  </si>
+  <si>
+    <t>LV9_ADJR2</t>
+  </si>
+  <si>
+    <t>LV10_ADJR2</t>
+  </si>
+  <si>
+    <t>LV11_ADJR2</t>
+  </si>
+  <si>
+    <t>LV12_ADJR2</t>
+  </si>
+  <si>
+    <t>LV13_ADJR2</t>
+  </si>
+  <si>
+    <t>LV14_ADJR2</t>
+  </si>
+  <si>
+    <t>LV15_ADJR2</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -40,7 +227,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -48,26 +235,80 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +350,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +382,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +417,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,2485 +593,2306 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_ADJR2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_ADJR2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_ADJR2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_ADJR2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_ADJR2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_ADJR2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_ADJR2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_ADJR2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_ADJR2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_ADJR2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_ADJR2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_ADJR2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_ADJR2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_ADJR2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_ADJR2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>-0.05290805228241284</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C2">
-        <v>-0.09443372468019953</v>
+        <v>-5.0760306089323887E-2</v>
       </c>
       <c r="D2">
-        <v>-0.09126380938006118</v>
+        <v>-9.1199064325587512E-2</v>
       </c>
       <c r="E2">
-        <v>-0.07399877926477888</v>
+        <v>-8.3781990948968196E-2</v>
       </c>
       <c r="F2">
-        <v>-0.09241042489189454</v>
+        <v>-6.8682454430213993E-2</v>
       </c>
       <c r="G2">
-        <v>-0.09754132334002058</v>
+        <v>-8.919582588805719E-2</v>
       </c>
       <c r="H2">
-        <v>-0.03574552227493137</v>
+        <v>-8.6743055952972409E-2</v>
       </c>
       <c r="I2">
-        <v>0.02164721650338609</v>
+        <v>-3.5100054229948392E-2</v>
       </c>
       <c r="J2">
-        <v>-0.015063840528667</v>
+        <v>1.544401461511313E-2</v>
       </c>
       <c r="K2">
-        <v>0.02926372003213416</v>
+        <v>-1.6114726880386239E-2</v>
       </c>
       <c r="L2">
-        <v>0.1126649665114977</v>
+        <v>3.618413635364133E-2</v>
       </c>
       <c r="M2">
-        <v>0.1431542778907424</v>
+        <v>0.1202218867928027</v>
       </c>
       <c r="N2">
-        <v>0.2506907001058479</v>
+        <v>0.1462236216641154</v>
       </c>
       <c r="O2">
-        <v>0.3376380698596818</v>
-      </c>
-      <c r="P2">
-        <v>0.3788698974968248</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.25914419563070012</v>
+      </c>
+      <c r="P2" s="2">
+        <v>0.34115933308270158</v>
+      </c>
+      <c r="Q2">
+        <v>0.3832416408084291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>-0.02338977500364611</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C3">
-        <v>-0.2005140104515762</v>
+        <v>-2.1784703184047419E-2</v>
       </c>
       <c r="D3">
-        <v>-0.1336381738029376</v>
+        <v>-0.1836540058058049</v>
       </c>
       <c r="E3">
-        <v>0.01189838638913479</v>
+        <v>-0.13080340504963039</v>
       </c>
       <c r="F3">
-        <v>0.09657643833166271</v>
+        <v>2.2779653551206459E-2</v>
       </c>
       <c r="G3">
-        <v>0.1503446018135401</v>
+        <v>9.9814043509296402E-2</v>
       </c>
       <c r="H3">
-        <v>0.2068370342305458</v>
-      </c>
-      <c r="I3">
-        <v>0.2308688696167036</v>
+        <v>0.14890806285852029</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.20945493222362879</v>
       </c>
       <c r="J3">
-        <v>0.2770922267672325</v>
+        <v>0.23082796084211499</v>
       </c>
       <c r="K3">
-        <v>0.3085641985620685</v>
+        <v>0.2709599888605983</v>
       </c>
       <c r="L3">
-        <v>0.3038172183834741</v>
+        <v>0.31275846893664377</v>
       </c>
       <c r="M3">
-        <v>0.3001693282739456</v>
+        <v>0.3061181032346651</v>
       </c>
       <c r="N3">
-        <v>0.2718381996675008</v>
+        <v>0.30544591984012121</v>
       </c>
       <c r="O3">
-        <v>0.2618310565870506</v>
+        <v>0.28323435450442691</v>
       </c>
       <c r="P3">
-        <v>0.279503503517157</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.27093730987138182</v>
+      </c>
+      <c r="Q3">
+        <v>0.28719961836556468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>-0.04284669174203476</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C4">
-        <v>-0.06111144707903767</v>
+        <v>-4.5551217912491809E-2</v>
       </c>
       <c r="D4">
-        <v>-0.1360344163531771</v>
+        <v>-7.0146657080181113E-2</v>
       </c>
       <c r="E4">
-        <v>-0.1330592574692104</v>
+        <v>-0.14142584219960491</v>
       </c>
       <c r="F4">
-        <v>-0.190699294789714</v>
+        <v>-0.14367005653628859</v>
       </c>
       <c r="G4">
-        <v>-0.08282408736231267</v>
+        <v>-0.20495449082784689</v>
       </c>
       <c r="H4">
-        <v>0.01328630784015385</v>
+        <v>-8.9073540246515565E-2</v>
       </c>
       <c r="I4">
-        <v>0.05917543654447908</v>
+        <v>-4.692850978129961E-4</v>
       </c>
       <c r="J4">
-        <v>0.06003981550784638</v>
+        <v>4.6372998811732798E-2</v>
       </c>
       <c r="K4">
-        <v>0.1288913429481977</v>
+        <v>5.1537844185087632E-2</v>
       </c>
       <c r="L4">
-        <v>0.2039273894455753</v>
-      </c>
-      <c r="M4">
-        <v>0.2686259895627419</v>
+        <v>0.1276897223456776</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0.20358189163539989</v>
       </c>
       <c r="N4">
-        <v>0.3006960808422869</v>
+        <v>0.26545666612773833</v>
       </c>
       <c r="O4">
-        <v>0.3044819192176816</v>
+        <v>0.29776492893527079</v>
       </c>
       <c r="P4">
-        <v>0.2883521766904626</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.30216416809106589</v>
+      </c>
+      <c r="Q4">
+        <v>0.28056876310679091</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>-0.03312243053805322</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C5">
-        <v>-0.1079856605714666</v>
+        <v>-3.6885823473918583E-2</v>
       </c>
       <c r="D5">
-        <v>-0.05459503733835094</v>
+        <v>-0.1053811149014181</v>
       </c>
       <c r="E5">
-        <v>-0.1533703686752588</v>
+        <v>-5.7751621718993493E-2</v>
       </c>
       <c r="F5">
-        <v>0.04500865097458354</v>
+        <v>-0.15253663812937851</v>
       </c>
       <c r="G5">
-        <v>0.1400691270995831</v>
+        <v>5.5014642971173519E-2</v>
       </c>
       <c r="H5">
-        <v>0.1693533787621279</v>
+        <v>0.1380503622450015</v>
       </c>
       <c r="I5">
-        <v>0.2433539035224793</v>
-      </c>
-      <c r="J5">
-        <v>0.3180588361562026</v>
+        <v>0.18631514700992119</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.26091803691187743</v>
       </c>
       <c r="K5">
-        <v>0.3489745368898847</v>
+        <v>0.32834674862810759</v>
       </c>
       <c r="L5">
-        <v>0.3763020465304757</v>
+        <v>0.35702876197566491</v>
       </c>
       <c r="M5">
-        <v>0.3728807720822171</v>
+        <v>0.38824581599612512</v>
       </c>
       <c r="N5">
-        <v>0.3450381085123029</v>
+        <v>0.3902592390644728</v>
       </c>
       <c r="O5">
-        <v>0.3228496262300383</v>
+        <v>0.36721647945261332</v>
       </c>
       <c r="P5">
-        <v>0.2982882160189979</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.34517765789021188</v>
+      </c>
+      <c r="Q5">
+        <v>0.32171564910436518</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>-0.0412546801920514</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C6">
-        <v>-0.1260005161593281</v>
+        <v>-3.3458454857208338E-2</v>
       </c>
       <c r="D6">
-        <v>-0.07472468280652299</v>
+        <v>-0.12645877462694899</v>
       </c>
       <c r="E6">
-        <v>-0.1059164955041367</v>
+        <v>-8.3177340287981322E-2</v>
       </c>
       <c r="F6">
-        <v>0.1220747841336962</v>
+        <v>-0.11424673681383481</v>
       </c>
       <c r="G6">
-        <v>0.2161262494102474</v>
+        <v>0.10614675802936439</v>
       </c>
       <c r="H6">
-        <v>0.274625959075315</v>
+        <v>0.20708049094883191</v>
       </c>
       <c r="I6">
-        <v>0.3459763203635748</v>
-      </c>
-      <c r="J6">
-        <v>0.3881054825802098</v>
+        <v>0.25395050616047349</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.33604012061313132</v>
       </c>
       <c r="K6">
-        <v>0.4035709836089361</v>
+        <v>0.37426636059640039</v>
       </c>
       <c r="L6">
-        <v>0.4237128868756384</v>
+        <v>0.38880005145138807</v>
       </c>
       <c r="M6">
-        <v>0.4230675376690948</v>
+        <v>0.40920128587936261</v>
       </c>
       <c r="N6">
-        <v>0.4141939030950981</v>
+        <v>0.41478442620314743</v>
       </c>
       <c r="O6">
-        <v>0.4177925070200631</v>
+        <v>0.40805496869326441</v>
       </c>
       <c r="P6">
-        <v>0.3980682099023356</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.41333752113135519</v>
+      </c>
+      <c r="Q6">
+        <v>0.39040734243706432</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>-0.04909751690350869</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C7">
-        <v>-0.07368020058378556</v>
+        <v>-4.8179409482328628E-2</v>
       </c>
       <c r="D7">
-        <v>-0.1418812321450352</v>
+        <v>-7.6567544327607887E-2</v>
       </c>
       <c r="E7">
-        <v>-0.1669177695781892</v>
+        <v>-0.1484933157258308</v>
       </c>
       <c r="F7">
-        <v>-0.2299105953192489</v>
+        <v>-0.1711848788498227</v>
       </c>
       <c r="G7">
-        <v>-0.1833269736810698</v>
+        <v>-0.2361387463398657</v>
       </c>
       <c r="H7">
-        <v>-0.06090437602934787</v>
+        <v>-0.18776839703561499</v>
       </c>
       <c r="I7">
-        <v>0.03096514335234958</v>
+        <v>-7.5852357566519854E-2</v>
       </c>
       <c r="J7">
-        <v>0.05937293358241082</v>
+        <v>2.3359720903310011E-2</v>
       </c>
       <c r="K7">
-        <v>0.07702919702022824</v>
+        <v>3.9868599231492413E-2</v>
       </c>
       <c r="L7">
-        <v>0.1663863395715355</v>
+        <v>6.6027888741920962E-2</v>
       </c>
       <c r="M7">
-        <v>0.2416368530020359</v>
-      </c>
-      <c r="N7">
-        <v>0.2913360647965413</v>
+        <v>0.17350668858813059</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0.25016054000684329</v>
       </c>
       <c r="O7">
-        <v>0.3198451662837478</v>
+        <v>0.3035423551825</v>
       </c>
       <c r="P7">
-        <v>0.3248471767528829</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.33041086411890852</v>
+      </c>
+      <c r="Q7">
+        <v>0.33374440533471522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>-0.04161676453248281</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C8">
-        <v>-0.07057973858627367</v>
+        <v>-4.2865679853720737E-2</v>
       </c>
       <c r="D8">
-        <v>-0.1416418503408551</v>
+        <v>-7.3799612970461254E-2</v>
       </c>
       <c r="E8">
-        <v>-0.1841140903868617</v>
+        <v>-0.13783896918590949</v>
       </c>
       <c r="F8">
-        <v>-0.1166499923587756</v>
+        <v>-0.1746833431637427</v>
       </c>
       <c r="G8">
-        <v>-0.01159558520438104</v>
+        <v>-0.12620351785038469</v>
       </c>
       <c r="H8">
-        <v>0.002520041407645938</v>
+        <v>-1.4728649980512791E-2</v>
       </c>
       <c r="I8">
-        <v>0.1065358913817624</v>
+        <v>-4.1507982933785721E-3</v>
       </c>
       <c r="J8">
-        <v>0.1443665198856982</v>
+        <v>0.101125755317307</v>
       </c>
       <c r="K8">
-        <v>0.2649601125690924</v>
-      </c>
-      <c r="L8">
-        <v>0.2852794860959212</v>
+        <v>0.14340464876690581</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0.26538554932171998</v>
       </c>
       <c r="M8">
-        <v>0.3309250211665597</v>
+        <v>0.2755446472300821</v>
       </c>
       <c r="N8">
-        <v>0.3553589923148683</v>
+        <v>0.32320003597498093</v>
       </c>
       <c r="O8">
-        <v>0.3554175993741479</v>
+        <v>0.34222753224146252</v>
       </c>
       <c r="P8">
-        <v>0.3380462752054358</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.34372223412262243</v>
+      </c>
+      <c r="Q8">
+        <v>0.32927516990087419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>-0.03607211251945654</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C9">
-        <v>-0.06618608712226508</v>
+        <v>-4.0532279859009368E-2</v>
       </c>
       <c r="D9">
-        <v>-0.1340323915188791</v>
+        <v>-6.8895938680059804E-2</v>
       </c>
       <c r="E9">
-        <v>-0.1582107314652124</v>
+        <v>-0.14281488912923121</v>
       </c>
       <c r="F9">
-        <v>-0.1084794204748157</v>
+        <v>-0.17352003752120559</v>
       </c>
       <c r="G9">
-        <v>-0.002529489497045312</v>
+        <v>-0.1181331106805579</v>
       </c>
       <c r="H9">
-        <v>0.01234063892225977</v>
+        <v>-1.0578793502869071E-2</v>
       </c>
       <c r="I9">
-        <v>0.1110449185537352</v>
+        <v>-5.4730212525314426E-3</v>
       </c>
       <c r="J9">
-        <v>0.1419693006268329</v>
+        <v>0.1009658819289611</v>
       </c>
       <c r="K9">
-        <v>0.2950826625093017</v>
-      </c>
-      <c r="L9">
-        <v>0.2914990300899696</v>
+        <v>0.12827336174814291</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0.28433867176451427</v>
       </c>
       <c r="M9">
-        <v>0.3361571278411464</v>
+        <v>0.27488063480842528</v>
       </c>
       <c r="N9">
-        <v>0.3652434933016384</v>
+        <v>0.31536399250923858</v>
       </c>
       <c r="O9">
-        <v>0.3584917404340695</v>
+        <v>0.3445134290959857</v>
       </c>
       <c r="P9">
-        <v>0.3574368941203659</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.34659050556300403</v>
+      </c>
+      <c r="Q9">
+        <v>0.34537125771537203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>-0.04436179603757923</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C10">
-        <v>-0.06975792298954113</v>
+        <v>-3.881136347182599E-2</v>
       </c>
       <c r="D10">
-        <v>-0.1358701835681856</v>
+        <v>-6.4423724284543279E-2</v>
       </c>
       <c r="E10">
-        <v>-0.1686031173526271</v>
+        <v>-0.12925042684661461</v>
       </c>
       <c r="F10">
-        <v>-0.1147508276794302</v>
+        <v>-0.1502293249044046</v>
       </c>
       <c r="G10">
-        <v>-0.01438681787367522</v>
+        <v>-0.1023211666714192</v>
       </c>
       <c r="H10">
-        <v>0.007647179935099677</v>
+        <v>2.3554811085064538E-3</v>
       </c>
       <c r="I10">
-        <v>0.10059765577667</v>
+        <v>1.6001848581917329E-2</v>
       </c>
       <c r="J10">
-        <v>0.1275128425245541</v>
+        <v>0.1115938013566264</v>
       </c>
       <c r="K10">
-        <v>0.2922363191494185</v>
-      </c>
-      <c r="L10">
-        <v>0.2738511236655062</v>
+        <v>0.13823641775081399</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0.28559346025603188</v>
       </c>
       <c r="M10">
-        <v>0.3191006949597484</v>
+        <v>0.27977382485151042</v>
       </c>
       <c r="N10">
-        <v>0.3520255984220851</v>
+        <v>0.32379828477001071</v>
       </c>
       <c r="O10">
-        <v>0.3425410242127466</v>
+        <v>0.3485492063317927</v>
       </c>
       <c r="P10">
-        <v>0.3450864745727094</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.34291843602730337</v>
+      </c>
+      <c r="Q10">
+        <v>0.33785971706853229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>-0.03969628540689529</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C11">
-        <v>-0.07027569620302593</v>
+        <v>-4.366716713564147E-2</v>
       </c>
       <c r="D11">
-        <v>-0.1420095071475113</v>
+        <v>-7.0464926842110656E-2</v>
       </c>
       <c r="E11">
-        <v>-0.1789542672539678</v>
+        <v>-0.1376703375147274</v>
       </c>
       <c r="F11">
-        <v>-0.1265133851181932</v>
+        <v>-0.17100811484458439</v>
       </c>
       <c r="G11">
-        <v>-0.01177472964020428</v>
+        <v>-0.1193990904740922</v>
       </c>
       <c r="H11">
-        <v>-0.006069604479411682</v>
+        <v>-2.2204968788808718E-2</v>
       </c>
       <c r="I11">
-        <v>0.1025672093118002</v>
+        <v>-1.5177226661513891E-2</v>
       </c>
       <c r="J11">
-        <v>0.1346634198528262</v>
+        <v>8.2197821973780727E-2</v>
       </c>
       <c r="K11">
-        <v>0.2911464398552266</v>
-      </c>
-      <c r="L11">
-        <v>0.2935264437604828</v>
+        <v>0.1146880110772161</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0.27667597002335748</v>
       </c>
       <c r="M11">
-        <v>0.3355304121454215</v>
+        <v>0.27990156185860021</v>
       </c>
       <c r="N11">
-        <v>0.3584664162819912</v>
+        <v>0.32280141611376839</v>
       </c>
       <c r="O11">
-        <v>0.3547477660320678</v>
+        <v>0.34709694575470512</v>
       </c>
       <c r="P11">
-        <v>0.3515386512891138</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.34555380593126528</v>
+      </c>
+      <c r="Q11">
+        <v>0.34798449098414391</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>-0.03463079357810216</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C12">
-        <v>-0.1078839043058302</v>
+        <v>-3.2698252750561818E-2</v>
       </c>
       <c r="D12">
-        <v>-0.05417091129565033</v>
+        <v>-9.2550325827629176E-2</v>
       </c>
       <c r="E12">
-        <v>-0.1577660157634831</v>
+        <v>-5.1827024442805437E-2</v>
       </c>
       <c r="F12">
-        <v>0.02697042290836315</v>
+        <v>-0.139847554582442</v>
       </c>
       <c r="G12">
-        <v>0.09240585211540442</v>
+        <v>2.9967042679074879E-2</v>
       </c>
       <c r="H12">
-        <v>0.2017873445031117</v>
+        <v>9.299508241695803E-2</v>
       </c>
       <c r="I12">
-        <v>0.3139854298249561</v>
+        <v>0.19649852697080869</v>
       </c>
       <c r="J12">
-        <v>0.3752649026421078</v>
-      </c>
-      <c r="K12">
-        <v>0.4056492773492207</v>
+        <v>0.29763549864281308</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0.35933573937250829</v>
       </c>
       <c r="L12">
-        <v>0.4381332842070349</v>
+        <v>0.38824782060962348</v>
       </c>
       <c r="M12">
-        <v>0.4418204208437044</v>
+        <v>0.41918248335403457</v>
       </c>
       <c r="N12">
-        <v>0.4232338586271515</v>
+        <v>0.42470336646426621</v>
       </c>
       <c r="O12">
-        <v>0.400803670778786</v>
+        <v>0.40463831315297188</v>
       </c>
       <c r="P12">
-        <v>0.3663172775784369</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.38701211053077011</v>
+      </c>
+      <c r="Q12">
+        <v>0.35066707113517048</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>-0.04913895576458739</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C13">
-        <v>-0.1894446586768078</v>
+        <v>-4.4289665153054728E-2</v>
       </c>
       <c r="D13">
-        <v>-0.1083141069980394</v>
+        <v>-0.1817010365798159</v>
       </c>
       <c r="E13">
-        <v>-0.1631794853789214</v>
+        <v>-0.113025325762863</v>
       </c>
       <c r="F13">
-        <v>-0.1526732075581596</v>
+        <v>-0.161394035301375</v>
       </c>
       <c r="G13">
-        <v>-0.008121960627003835</v>
+        <v>-0.1591108403428787</v>
       </c>
       <c r="H13">
-        <v>-0.004027723758629883</v>
+        <v>-1.319739024232556E-2</v>
       </c>
       <c r="I13">
-        <v>0.04656211036215085</v>
+        <v>-3.1407553632258321E-3</v>
       </c>
       <c r="J13">
-        <v>0.1196291661391423</v>
+        <v>4.7578530694834052E-2</v>
       </c>
       <c r="K13">
-        <v>0.1998711389252365</v>
-      </c>
-      <c r="L13">
-        <v>0.2088850523414891</v>
+        <v>0.12901632299170629</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0.20478002844279</v>
       </c>
       <c r="M13">
-        <v>0.2319156624246561</v>
+        <v>0.2181745254977846</v>
       </c>
       <c r="N13">
-        <v>0.2378089985964852</v>
+        <v>0.2436295714090608</v>
       </c>
       <c r="O13">
-        <v>0.2551540197076285</v>
+        <v>0.24536032016385351</v>
       </c>
       <c r="P13">
-        <v>0.2482487881448249</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.26801173258871891</v>
+      </c>
+      <c r="Q13">
+        <v>0.25790170399893247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>-0.04808359499714974</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C14">
-        <v>-0.06989451551362991</v>
+        <v>-4.4941082695398787E-2</v>
       </c>
       <c r="D14">
-        <v>-0.135959239701734</v>
+        <v>-7.0516358848907709E-2</v>
       </c>
       <c r="E14">
-        <v>-0.1530254182300488</v>
+        <v>-0.13956289655248169</v>
       </c>
       <c r="F14">
-        <v>-0.218464555562508</v>
+        <v>-0.1638220760658626</v>
       </c>
       <c r="G14">
-        <v>-0.169145337263429</v>
+        <v>-0.22107747327379379</v>
       </c>
       <c r="H14">
-        <v>-0.06452942683433709</v>
+        <v>-0.17251964610350889</v>
       </c>
       <c r="I14">
-        <v>0.02753580605314067</v>
+        <v>-6.7934558172047813E-2</v>
       </c>
       <c r="J14">
-        <v>0.04629384918900507</v>
+        <v>2.121720329641617E-2</v>
       </c>
       <c r="K14">
-        <v>0.07711068128583996</v>
+        <v>5.1137525793332729E-2</v>
       </c>
       <c r="L14">
-        <v>0.1819680445369365</v>
+        <v>7.1829807608517926E-2</v>
       </c>
       <c r="M14">
-        <v>0.2957630443815167</v>
-      </c>
-      <c r="N14">
-        <v>0.3294373927558531</v>
+        <v>0.18083751760259881</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0.28875856947630679</v>
       </c>
       <c r="O14">
-        <v>0.3582996416016226</v>
+        <v>0.32975530285487797</v>
       </c>
       <c r="P14">
-        <v>0.3841058031065498</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.35743453031196898</v>
+      </c>
+      <c r="Q14">
+        <v>0.38041072501968359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>-0.05173732756432053</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C15">
-        <v>-0.07387379987922124</v>
+        <v>-4.1627696416332169E-2</v>
       </c>
       <c r="D15">
-        <v>-0.1391800687413293</v>
+        <v>-6.5622536011725158E-2</v>
       </c>
       <c r="E15">
-        <v>-0.1551677339159435</v>
+        <v>-0.1285622969038375</v>
       </c>
       <c r="F15">
-        <v>-0.2207788171001067</v>
+        <v>-0.14346655767922201</v>
       </c>
       <c r="G15">
-        <v>-0.1768674468017014</v>
+        <v>-0.19310627649916989</v>
       </c>
       <c r="H15">
-        <v>-0.06427439069833051</v>
+        <v>-0.15064894828310671</v>
       </c>
       <c r="I15">
-        <v>0.008967489720978114</v>
+        <v>-4.4061013989195409E-2</v>
       </c>
       <c r="J15">
-        <v>0.0355495575624754</v>
+        <v>2.3678949656459568E-2</v>
       </c>
       <c r="K15">
-        <v>0.06604659091536197</v>
+        <v>5.4301471979794153E-2</v>
       </c>
       <c r="L15">
-        <v>0.1610332049896535</v>
+        <v>6.6875719593464042E-2</v>
       </c>
       <c r="M15">
-        <v>0.2635891532491328</v>
-      </c>
-      <c r="N15">
-        <v>0.3041205993509052</v>
+        <v>0.16039490477855409</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.26492563194174018</v>
       </c>
       <c r="O15">
-        <v>0.3269921843701484</v>
+        <v>0.30367351218477651</v>
       </c>
       <c r="P15">
-        <v>0.3508115932889619</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.32730218802155497</v>
+      </c>
+      <c r="Q15">
+        <v>0.34639377755754092</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>-0.04446687221492021</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C16">
-        <v>-0.06678599886700115</v>
+        <v>-4.8659621993792958E-2</v>
       </c>
       <c r="D16">
-        <v>-0.133092069592516</v>
+        <v>-7.5266989944081972E-2</v>
       </c>
       <c r="E16">
-        <v>-0.1482428139168927</v>
+        <v>-0.1395947013974955</v>
       </c>
       <c r="F16">
-        <v>-0.2061264177841818</v>
+        <v>-0.1567609807903399</v>
       </c>
       <c r="G16">
-        <v>-0.1730224609137091</v>
+        <v>-0.21159874100949469</v>
       </c>
       <c r="H16">
-        <v>-0.0734038769405486</v>
+        <v>-0.1659135775675725</v>
       </c>
       <c r="I16">
-        <v>0.0166553908256215</v>
+        <v>-5.8494323700376098E-2</v>
       </c>
       <c r="J16">
-        <v>0.0475133385834572</v>
+        <v>2.5575182192896961E-2</v>
       </c>
       <c r="K16">
-        <v>0.06818775118554771</v>
+        <v>4.5727510327543387E-2</v>
       </c>
       <c r="L16">
-        <v>0.1548809851226439</v>
+        <v>6.1648822174612178E-2</v>
       </c>
       <c r="M16">
-        <v>0.2613204978487133</v>
-      </c>
-      <c r="N16">
-        <v>0.3093014510542076</v>
+        <v>0.15332715027264279</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0.26114016964458459</v>
       </c>
       <c r="O16">
-        <v>0.3427064481324353</v>
+        <v>0.30466088098539168</v>
       </c>
       <c r="P16">
-        <v>0.3609336804059985</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.33725627131746488</v>
+      </c>
+      <c r="Q16">
+        <v>0.35849317911355111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>-0.04572540764015506</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C17">
-        <v>-0.07038254004729758</v>
+        <v>-4.3867541925287537E-2</v>
       </c>
       <c r="D17">
-        <v>-0.1386711192880916</v>
+        <v>-6.2440217216917213E-2</v>
       </c>
       <c r="E17">
-        <v>-0.1568524062136908</v>
+        <v>-0.12748287663450389</v>
       </c>
       <c r="F17">
-        <v>-0.206877199238727</v>
+        <v>-0.14364474690088661</v>
       </c>
       <c r="G17">
-        <v>-0.1757930834748187</v>
+        <v>-0.20538544676058579</v>
       </c>
       <c r="H17">
-        <v>-0.06828710596107077</v>
+        <v>-0.16306792612764981</v>
       </c>
       <c r="I17">
-        <v>0.02163875727083334</v>
+        <v>-6.577448443359242E-2</v>
       </c>
       <c r="J17">
-        <v>0.03663451699610781</v>
+        <v>6.9879344634859574E-3</v>
       </c>
       <c r="K17">
-        <v>0.05192965616571688</v>
+        <v>4.1939314651794693E-2</v>
       </c>
       <c r="L17">
-        <v>0.1318304182993638</v>
+        <v>4.8595898675979479E-2</v>
       </c>
       <c r="M17">
-        <v>0.2347247332788081</v>
-      </c>
-      <c r="N17">
-        <v>0.2687167490995103</v>
+        <v>0.13870225669820299</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.23727066899107649</v>
       </c>
       <c r="O17">
-        <v>0.3007002963299792</v>
+        <v>0.27737230732676832</v>
       </c>
       <c r="P17">
-        <v>0.319515690843322</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.3065013182020716</v>
+      </c>
+      <c r="Q17">
+        <v>0.33745507773715178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>-0.03324441172796238</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C18">
-        <v>-0.1118730612158209</v>
+        <v>-3.4828627683201878E-2</v>
       </c>
       <c r="D18">
-        <v>-0.05671004413398258</v>
+        <v>-0.1045636705630829</v>
       </c>
       <c r="E18">
-        <v>-0.1638915953642507</v>
+        <v>-5.0418403695272757E-2</v>
       </c>
       <c r="F18">
-        <v>0.06233836615829329</v>
+        <v>-0.1523259528739434</v>
       </c>
       <c r="G18">
-        <v>0.1398011461922044</v>
+        <v>5.8053909062709609E-2</v>
       </c>
       <c r="H18">
-        <v>0.216513369919801</v>
+        <v>0.12810909225448361</v>
       </c>
       <c r="I18">
-        <v>0.3064404133723341</v>
-      </c>
-      <c r="J18">
-        <v>0.3702879597033081</v>
+        <v>0.20497934289865519</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.29755671569032988</v>
       </c>
       <c r="K18">
-        <v>0.3896170179771431</v>
+        <v>0.36682457826949938</v>
       </c>
       <c r="L18">
-        <v>0.4150460230905172</v>
+        <v>0.38262705951309961</v>
       </c>
       <c r="M18">
-        <v>0.4233206098792783</v>
+        <v>0.40882698703008602</v>
       </c>
       <c r="N18">
-        <v>0.3950193390999827</v>
+        <v>0.41362358920929748</v>
       </c>
       <c r="O18">
-        <v>0.3724735410620446</v>
+        <v>0.38564343722491878</v>
       </c>
       <c r="P18">
-        <v>0.3512037421869109</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.36559283100493561</v>
+      </c>
+      <c r="Q18">
+        <v>0.34314902759993032</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>-0.03747800578326006</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C19">
-        <v>-0.1391249362925348</v>
+        <v>-4.6012679597663621E-2</v>
       </c>
       <c r="D19">
-        <v>-0.09751963475036297</v>
+        <v>-0.14035944974364581</v>
       </c>
       <c r="E19">
-        <v>-0.1485559962969978</v>
+        <v>-9.8851422293065705E-2</v>
       </c>
       <c r="F19">
-        <v>0.1110496794115079</v>
+        <v>-0.1345156227069467</v>
       </c>
       <c r="G19">
-        <v>0.1955476426615595</v>
+        <v>0.11530534819230789</v>
       </c>
       <c r="H19">
-        <v>0.2696519303855587</v>
+        <v>0.20330690642922231</v>
       </c>
       <c r="I19">
-        <v>0.3502012457951503</v>
-      </c>
-      <c r="J19">
-        <v>0.3964427780747922</v>
+        <v>0.261130302453916</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.34572791440842171</v>
       </c>
       <c r="K19">
-        <v>0.4092652347595571</v>
+        <v>0.39615483170196408</v>
       </c>
       <c r="L19">
-        <v>0.4322564284528748</v>
+        <v>0.40888454225104831</v>
       </c>
       <c r="M19">
-        <v>0.4346961299285406</v>
+        <v>0.4358816083362711</v>
       </c>
       <c r="N19">
-        <v>0.4277818462249921</v>
+        <v>0.4327571423850296</v>
       </c>
       <c r="O19">
-        <v>0.4293157470341715</v>
+        <v>0.42092898557003489</v>
       </c>
       <c r="P19">
-        <v>0.4167370986831489</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.4278558933951514</v>
+      </c>
+      <c r="Q19">
+        <v>0.41943105355089177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>-0.03691273779090792</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C20">
-        <v>-0.1470038550428452</v>
+        <v>-3.8548549759861758E-2</v>
       </c>
       <c r="D20">
-        <v>-0.1084806214982054</v>
+        <v>-0.14832249787934559</v>
       </c>
       <c r="E20">
-        <v>-0.01817334624716794</v>
+        <v>-0.1083076597568321</v>
       </c>
       <c r="F20">
-        <v>0.09132960517714807</v>
+        <v>-1.8583072622637382E-2</v>
       </c>
       <c r="G20">
-        <v>0.1161355191973046</v>
+        <v>0.102225506552204</v>
       </c>
       <c r="H20">
-        <v>0.213492732844479</v>
+        <v>0.1385090345044199</v>
       </c>
       <c r="I20">
-        <v>0.2985283521661848</v>
+        <v>0.2370932521753743</v>
       </c>
       <c r="J20">
-        <v>0.3401266851169133</v>
-      </c>
-      <c r="K20">
-        <v>0.384463531495526</v>
+        <v>0.31220785456573558</v>
+      </c>
+      <c r="K20" s="2">
+        <v>0.34863602721189962</v>
       </c>
       <c r="L20">
-        <v>0.3931755789314696</v>
+        <v>0.39737718327380211</v>
       </c>
       <c r="M20">
-        <v>0.3972897706299507</v>
+        <v>0.40040475349846938</v>
       </c>
       <c r="N20">
-        <v>0.4365706518777309</v>
+        <v>0.40594456119222289</v>
       </c>
       <c r="O20">
-        <v>0.4371537737006476</v>
+        <v>0.44241881584017978</v>
       </c>
       <c r="P20">
-        <v>0.4331722122125704</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.44463936349094241</v>
+      </c>
+      <c r="Q20">
+        <v>0.44738082111383298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>-0.02334707594584574</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C21">
-        <v>-0.1866885854365806</v>
+        <v>-2.3986836621994918E-2</v>
       </c>
       <c r="D21">
-        <v>-0.1348516536432175</v>
+        <v>-0.1933722877724626</v>
       </c>
       <c r="E21">
-        <v>-0.01362758374560175</v>
+        <v>-0.13727698363590429</v>
       </c>
       <c r="F21">
-        <v>0.05189538556187615</v>
+        <v>-1.146466511697769E-2</v>
       </c>
       <c r="G21">
-        <v>0.08137399859106378</v>
+        <v>5.9077058142668858E-2</v>
       </c>
       <c r="H21">
-        <v>0.1363534809165156</v>
+        <v>9.0834699351538539E-2</v>
       </c>
       <c r="I21">
-        <v>0.1771938216111085</v>
-      </c>
-      <c r="J21">
-        <v>0.2567529391222927</v>
+        <v>0.1418509080373957</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.19453542296391721</v>
       </c>
       <c r="K21">
-        <v>0.2923893779586585</v>
+        <v>0.26453035875043929</v>
       </c>
       <c r="L21">
-        <v>0.3083295716797268</v>
+        <v>0.3007866804685666</v>
       </c>
       <c r="M21">
-        <v>0.2923539091645606</v>
+        <v>0.31412155688861032</v>
       </c>
       <c r="N21">
-        <v>0.2604942805217176</v>
+        <v>0.29967743713258022</v>
       </c>
       <c r="O21">
-        <v>0.2391474668012656</v>
+        <v>0.26077383937920562</v>
       </c>
       <c r="P21">
-        <v>0.2489051300180812</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.23765436570944981</v>
+      </c>
+      <c r="Q21">
+        <v>0.24955042209503189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>-0.02325415210536802</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C22">
-        <v>-0.1831882922030569</v>
+        <v>-2.4607947014113399E-2</v>
       </c>
       <c r="D22">
-        <v>-0.127459371179816</v>
+        <v>-0.18411424604785079</v>
       </c>
       <c r="E22">
-        <v>0.007992810066180769</v>
+        <v>-0.1290674248820759</v>
       </c>
       <c r="F22">
-        <v>0.06220966402277672</v>
+        <v>-1.444957127082154E-3</v>
       </c>
       <c r="G22">
-        <v>0.0816210658440438</v>
+        <v>5.1378181697079063E-2</v>
       </c>
       <c r="H22">
-        <v>0.1098006311829662</v>
+        <v>7.7234929345367298E-2</v>
       </c>
       <c r="I22">
-        <v>0.1286881853650334</v>
+        <v>0.1018220505065623</v>
       </c>
       <c r="J22">
-        <v>0.1970431490551278</v>
-      </c>
-      <c r="K22">
-        <v>0.2387557792789214</v>
+        <v>0.1219006826227986</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0.1955586688494432</v>
       </c>
       <c r="L22">
-        <v>0.2487954062366608</v>
+        <v>0.23803099272159811</v>
       </c>
       <c r="M22">
-        <v>0.2537606883678765</v>
+        <v>0.26140724899842599</v>
       </c>
       <c r="N22">
-        <v>0.2351152877833493</v>
+        <v>0.27256556506457358</v>
       </c>
       <c r="O22">
-        <v>0.2294834846096992</v>
+        <v>0.25481874645357638</v>
       </c>
       <c r="P22">
-        <v>0.2278860071787833</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.2479236019785501</v>
+      </c>
+      <c r="Q22">
+        <v>0.24289508261368811</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>-0.03326489323889399</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C23">
-        <v>-0.1474635156474074</v>
+        <v>-3.3966391673629658E-2</v>
       </c>
       <c r="D23">
-        <v>-0.02314808568866851</v>
+        <v>-0.1534015392222027</v>
       </c>
       <c r="E23">
-        <v>0.07485751941415114</v>
+        <v>-3.6124300470172593E-2</v>
       </c>
       <c r="F23">
-        <v>0.2188420234410349</v>
+        <v>7.3634047482709089E-2</v>
       </c>
       <c r="G23">
-        <v>0.3077272637854153</v>
+        <v>0.20798300500296521</v>
       </c>
       <c r="H23">
-        <v>0.3399794976089098</v>
+        <v>0.29443301258018811</v>
       </c>
       <c r="I23">
-        <v>0.3571745328183165</v>
-      </c>
-      <c r="J23">
-        <v>0.3749224052706703</v>
+        <v>0.32524747594897169</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0.33875630482770203</v>
       </c>
       <c r="K23">
-        <v>0.3690144964077461</v>
+        <v>0.36211836408806453</v>
       </c>
       <c r="L23">
-        <v>0.3623151035989185</v>
+        <v>0.36832104909139618</v>
       </c>
       <c r="M23">
-        <v>0.3464388218896167</v>
+        <v>0.36850020782208792</v>
       </c>
       <c r="N23">
-        <v>0.3404914154570606</v>
+        <v>0.35696910693012379</v>
       </c>
       <c r="O23">
-        <v>0.3365238836832425</v>
+        <v>0.3485159217783183</v>
       </c>
       <c r="P23">
-        <v>0.3188225708429545</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.35099532299303909</v>
+      </c>
+      <c r="Q23">
+        <v>0.32862867708809612</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>-0.0370486411866286</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C24">
-        <v>-0.002002338917554252</v>
+        <v>-7.1858544647608727E-2</v>
       </c>
       <c r="D24">
-        <v>0.0593246667256266</v>
+        <v>-0.1328441396214928</v>
       </c>
       <c r="E24">
-        <v>-0.01286902784468373</v>
+        <v>-0.19259433769453591</v>
       </c>
       <c r="F24">
-        <v>-0.03004712281138446</v>
+        <v>-0.149493303370002</v>
       </c>
       <c r="G24">
-        <v>-0.08407976969448257</v>
+        <v>-0.13111711532549189</v>
       </c>
       <c r="H24">
-        <v>-0.07419585036678883</v>
+        <v>-7.6565447075566895E-2</v>
       </c>
       <c r="I24">
-        <v>-0.1008812543978504</v>
+        <v>-0.1190332419221726</v>
       </c>
       <c r="J24">
-        <v>-0.178393088025166</v>
-      </c>
-      <c r="K24">
-        <v>-0.3247751908932399</v>
+        <v>-6.727013778044498E-2</v>
+      </c>
+      <c r="K24" s="2">
+        <v>9.3147234878773744E-2</v>
       </c>
       <c r="L24">
-        <v>-0.3172201425195671</v>
+        <v>0.19011204258841211</v>
       </c>
       <c r="M24">
-        <v>-0.3514604612904817</v>
+        <v>0.2191681014158311</v>
       </c>
       <c r="N24">
-        <v>-0.4465053461935007</v>
+        <v>0.19842144357744901</v>
       </c>
       <c r="O24">
-        <v>-0.5200335447926415</v>
+        <v>0.13490403418338581</v>
       </c>
       <c r="P24">
-        <v>-0.6291734173444817</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>7.3851842915175797E-2</v>
+      </c>
+      <c r="Q24">
+        <v>-9.9235247514425553E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>-0.1538840890504211</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C25">
-        <v>-0.09835657641436843</v>
+        <v>-6.9359185286404113E-2</v>
       </c>
       <c r="D25">
-        <v>-0.108564905364894</v>
+        <v>-0.1275483732043034</v>
       </c>
       <c r="E25">
-        <v>-0.08699783951237511</v>
+        <v>-0.1879707532806788</v>
       </c>
       <c r="F25">
-        <v>-0.140048370301564</v>
+        <v>-0.13910606036587411</v>
       </c>
       <c r="G25">
-        <v>-0.2098346658443764</v>
+        <v>-0.11746465444103429</v>
       </c>
       <c r="H25">
-        <v>-0.2100571360642921</v>
+        <v>-0.10019322616698401</v>
       </c>
       <c r="I25">
-        <v>-0.1694189313138173</v>
+        <v>-0.20190270583851749</v>
       </c>
       <c r="J25">
-        <v>-0.211016939092021</v>
+        <v>-0.14489780202162261</v>
       </c>
       <c r="K25">
-        <v>-0.3059412987308206</v>
-      </c>
-      <c r="L25">
-        <v>-0.3597690442681866</v>
+        <v>-5.5739541062734883E-2</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0.1522620686275685</v>
       </c>
       <c r="M25">
-        <v>-0.4557987830411551</v>
+        <v>0.1840377222761681</v>
       </c>
       <c r="N25">
-        <v>-0.5670208490379525</v>
+        <v>0.19928739929864489</v>
       </c>
       <c r="O25">
-        <v>-0.6198940909768101</v>
+        <v>0.1583043520776041</v>
       </c>
       <c r="P25">
-        <v>-0.6587941394194393</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.10599419737483839</v>
+      </c>
+      <c r="Q25">
+        <v>3.583851082120685E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>-0.06769430620935225</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C26">
-        <v>-0.03155757069003649</v>
+        <v>-6.7730587431052106E-2</v>
       </c>
       <c r="D26">
-        <v>0.04522458476251937</v>
+        <v>-0.13000919475617459</v>
       </c>
       <c r="E26">
-        <v>0.06624728714623514</v>
+        <v>-0.14373763914635951</v>
       </c>
       <c r="F26">
-        <v>0.0795219230494283</v>
+        <v>-8.5017289794046533E-2</v>
       </c>
       <c r="G26">
-        <v>0.1146046092465791</v>
+        <v>-0.12343693877134181</v>
       </c>
       <c r="H26">
-        <v>0.127984095746262</v>
+        <v>-9.0197564755229651E-2</v>
       </c>
       <c r="I26">
-        <v>0.1319066326383232</v>
+        <v>2.720956550588224E-2</v>
       </c>
       <c r="J26">
-        <v>0.1682671328457477</v>
-      </c>
-      <c r="K26">
-        <v>0.200951297503126</v>
+        <v>-4.8416731099570072E-2</v>
+      </c>
+      <c r="K26" s="2">
+        <v>9.5726021734760344E-2</v>
       </c>
       <c r="L26">
-        <v>0.1704369540537203</v>
+        <v>0.1840070224259234</v>
       </c>
       <c r="M26">
-        <v>0.1894170947358043</v>
+        <v>0.197873808564419</v>
       </c>
       <c r="N26">
-        <v>0.1624707189988563</v>
+        <v>0.17485262065527651</v>
       </c>
       <c r="O26">
-        <v>0.1391649537943931</v>
+        <v>0.14239668000995101</v>
       </c>
       <c r="P26">
-        <v>0.1390933831178851</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>8.2395939595485981E-2</v>
+      </c>
+      <c r="Q26">
+        <v>-4.4994142413409153E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>-0.1177491306962131</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C27">
-        <v>-0.07936111006377729</v>
+        <v>-6.9488828602768241E-2</v>
       </c>
       <c r="D27">
-        <v>0.1127821438566732</v>
+        <v>-0.13147458805587309</v>
       </c>
       <c r="E27">
-        <v>0.123417757396492</v>
+        <v>-0.14454314046976841</v>
       </c>
       <c r="F27">
-        <v>0.1095093909276492</v>
+        <v>-7.9386756976424458E-2</v>
       </c>
       <c r="G27">
-        <v>0.1031714104304308</v>
+        <v>-0.11887701638977929</v>
       </c>
       <c r="H27">
-        <v>0.09469399050862776</v>
+        <v>-9.1450436018570933E-2</v>
       </c>
       <c r="I27">
-        <v>0.05453247405299823</v>
+        <v>5.1256079097461481E-3</v>
       </c>
       <c r="J27">
-        <v>0.100349875513952</v>
+        <v>-4.9073370827019631E-2</v>
       </c>
       <c r="K27">
-        <v>0.1131704319528543</v>
-      </c>
-      <c r="L27">
-        <v>0.1453961880174355</v>
+        <v>7.4895897482644289E-2</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0.20921687259205271</v>
       </c>
       <c r="M27">
-        <v>0.1852858585269195</v>
+        <v>0.25936439106711878</v>
       </c>
       <c r="N27">
-        <v>0.1845330164842662</v>
+        <v>0.29167872878824558</v>
       </c>
       <c r="O27">
-        <v>0.1556550667037256</v>
+        <v>0.31017139390362991</v>
       </c>
       <c r="P27">
-        <v>0.137946300435039</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.28348179650566302</v>
+      </c>
+      <c r="Q27">
+        <v>0.27685180081345617</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>-0.06329911698764076</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C28">
-        <v>-0.1172730905491431</v>
+        <v>-6.5067720490229602E-2</v>
       </c>
       <c r="D28">
-        <v>-0.1726349806042995</v>
+        <v>-0.1188209735978909</v>
       </c>
       <c r="E28">
-        <v>-0.1323277613228747</v>
+        <v>-0.1698063556419091</v>
       </c>
       <c r="F28">
-        <v>-0.114476221805836</v>
+        <v>-0.12753098546736341</v>
       </c>
       <c r="G28">
-        <v>-0.05941504249098294</v>
+        <v>-0.108638314943881</v>
       </c>
       <c r="H28">
-        <v>-0.1111156245582142</v>
+        <v>-9.0487052984105643E-2</v>
       </c>
       <c r="I28">
-        <v>-0.05073479102647779</v>
+        <v>-0.15601152801020629</v>
       </c>
       <c r="J28">
-        <v>0.07661386684639469</v>
+        <v>-0.13210531162208181</v>
       </c>
       <c r="K28">
-        <v>0.1949439467972967</v>
-      </c>
-      <c r="L28">
-        <v>0.2283541557249358</v>
+        <v>-6.8297247425719465E-2</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0.15705516650328491</v>
       </c>
       <c r="M28">
-        <v>0.2024768790704259</v>
+        <v>0.2026701550898124</v>
       </c>
       <c r="N28">
-        <v>0.1449732336300049</v>
+        <v>0.23226084738517949</v>
       </c>
       <c r="O28">
-        <v>0.08638835057250774</v>
+        <v>0.24202019468594391</v>
       </c>
       <c r="P28">
-        <v>0.003409890382122684</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.24571166286576859</v>
+      </c>
+      <c r="Q28">
+        <v>0.23718763369396001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
       </c>
       <c r="B29">
-        <v>-0.07196788188040387</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C29">
-        <v>-0.1263451147757606</v>
+        <v>-6.8512567829549079E-2</v>
       </c>
       <c r="D29">
-        <v>-0.1853313620109306</v>
+        <v>-0.1257885359990259</v>
       </c>
       <c r="E29">
-        <v>-0.1390069977771699</v>
+        <v>-0.18256838385234911</v>
       </c>
       <c r="F29">
-        <v>-0.1158826113618496</v>
+        <v>-0.13982442189672101</v>
       </c>
       <c r="G29">
-        <v>-0.09576157281215598</v>
+        <v>-0.1163912176281334</v>
       </c>
       <c r="H29">
-        <v>-0.1871818630358159</v>
+        <v>-9.4802083974037527E-2</v>
       </c>
       <c r="I29">
-        <v>-0.1177998441673866</v>
+        <v>-0.16031497256999511</v>
       </c>
       <c r="J29">
-        <v>-0.0398165057973842</v>
+        <v>-0.13414904264095051</v>
       </c>
       <c r="K29">
-        <v>0.163011923642781</v>
-      </c>
-      <c r="L29">
-        <v>0.1946879863177405</v>
+        <v>-7.0586245094377387E-2</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0.141956344739886</v>
       </c>
       <c r="M29">
-        <v>0.2148545580193736</v>
+        <v>0.19518619899985559</v>
       </c>
       <c r="N29">
-        <v>0.1884002797957192</v>
+        <v>0.23729070239233971</v>
       </c>
       <c r="O29">
-        <v>0.1367678550590751</v>
+        <v>0.25098601316714969</v>
       </c>
       <c r="P29">
-        <v>0.0720583866840119</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.26057631671746978</v>
+      </c>
+      <c r="Q29">
+        <v>0.27204286004660078</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>45</v>
       </c>
       <c r="B30">
-        <v>-0.06820513997892169</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C30">
-        <v>-0.1284330252703835</v>
+        <v>-7.1212799957591916E-2</v>
       </c>
       <c r="D30">
-        <v>-0.1413239421058464</v>
+        <v>-0.127368887631229</v>
       </c>
       <c r="E30">
-        <v>-0.08127428697157131</v>
+        <v>-0.1747719583256257</v>
       </c>
       <c r="F30">
-        <v>-0.1285553506051062</v>
+        <v>-0.13326718222898021</v>
       </c>
       <c r="G30">
-        <v>-0.09174131883287052</v>
+        <v>-0.1115701096274733</v>
       </c>
       <c r="H30">
-        <v>0.008786651344780299</v>
+        <v>-9.292343232174699E-2</v>
       </c>
       <c r="I30">
-        <v>-0.05189460781608334</v>
+        <v>-0.1530618203678962</v>
       </c>
       <c r="J30">
-        <v>0.08542049197444349</v>
+        <v>-0.1207557500223258</v>
       </c>
       <c r="K30">
-        <v>0.1746613578725859</v>
-      </c>
-      <c r="L30">
-        <v>0.1920376319685743</v>
+        <v>-7.0239183398508265E-2</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0.14086259189315189</v>
       </c>
       <c r="M30">
-        <v>0.172775812508089</v>
+        <v>0.1965092148556713</v>
       </c>
       <c r="N30">
-        <v>0.1366976301183994</v>
+        <v>0.2343706584232918</v>
       </c>
       <c r="O30">
-        <v>0.07136848068773059</v>
+        <v>0.25478579331619838</v>
       </c>
       <c r="P30">
-        <v>-0.01427525921144917</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.27248032003499911</v>
+      </c>
+      <c r="Q30">
+        <v>0.28322408082184197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>-0.0687066357074681</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C31">
-        <v>-0.135707065632097</v>
+        <v>-6.3516947428013171E-2</v>
       </c>
       <c r="D31">
-        <v>-0.1502166609367696</v>
+        <v>-0.1131046384313398</v>
       </c>
       <c r="E31">
-        <v>-0.09180169800958521</v>
+        <v>-0.16805298918487629</v>
       </c>
       <c r="F31">
-        <v>-0.1263864416903532</v>
+        <v>-0.1243617123525932</v>
       </c>
       <c r="G31">
-        <v>-0.09989851253912074</v>
+        <v>-0.10607497413656999</v>
       </c>
       <c r="H31">
-        <v>0.001074478903998269</v>
+        <v>-8.7629763293037705E-2</v>
       </c>
       <c r="I31">
-        <v>-0.07005202890519824</v>
+        <v>-0.1525507869246332</v>
       </c>
       <c r="J31">
-        <v>0.0534211817714293</v>
+        <v>-0.14131360695189729</v>
       </c>
       <c r="K31">
-        <v>0.1904718640678876</v>
-      </c>
-      <c r="L31">
-        <v>0.2506366605116656</v>
+        <v>-8.9935786277619445E-2</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0.1149308881575259</v>
       </c>
       <c r="M31">
-        <v>0.2857865796363692</v>
+        <v>0.17204870321328261</v>
       </c>
       <c r="N31">
-        <v>0.3004243207230871</v>
+        <v>0.20397271852992591</v>
       </c>
       <c r="O31">
-        <v>0.2713710449747959</v>
+        <v>0.23840462669948359</v>
       </c>
       <c r="P31">
-        <v>0.2672551840714792</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.25183759857675941</v>
+      </c>
+      <c r="Q31">
+        <v>0.27269776863783779</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>-0.06859594505090771</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C32">
-        <v>-0.1213314881623955</v>
+        <v>-6.4725790130664096E-2</v>
       </c>
       <c r="D32">
-        <v>-0.1771534559419858</v>
+        <v>-0.12173632301152219</v>
       </c>
       <c r="E32">
-        <v>-0.1318607279293235</v>
+        <v>-0.17762849941848369</v>
       </c>
       <c r="F32">
-        <v>-0.112314809775858</v>
+        <v>-0.13347995301150231</v>
       </c>
       <c r="G32">
-        <v>-0.09721119758310341</v>
+        <v>-0.1086701185987885</v>
       </c>
       <c r="H32">
-        <v>-0.1641335290817526</v>
+        <v>-8.4833057056379751E-2</v>
       </c>
       <c r="I32">
-        <v>-0.1334759373032734</v>
+        <v>-0.1478442053649798</v>
       </c>
       <c r="J32">
-        <v>-0.06980341848804239</v>
+        <v>-0.1150327636611633</v>
       </c>
       <c r="K32">
-        <v>0.1347600666480338</v>
-      </c>
-      <c r="L32">
-        <v>0.1934858914475964</v>
+        <v>-5.1093589707120683E-2</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0.17191473748712471</v>
       </c>
       <c r="M32">
-        <v>0.222730969920941</v>
+        <v>0.21303965636470171</v>
       </c>
       <c r="N32">
-        <v>0.243882766536665</v>
+        <v>0.23740773559422501</v>
       </c>
       <c r="O32">
-        <v>0.2423485232288732</v>
+        <v>0.23771189200381851</v>
       </c>
       <c r="P32">
-        <v>0.2439521585617673</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.22433759205169479</v>
+      </c>
+      <c r="Q32">
+        <v>0.21161783003019849</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>-0.07036897738487652</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C33">
-        <v>-0.1263309138545374</v>
+        <v>-7.0702132126642461E-2</v>
       </c>
       <c r="D33">
-        <v>-0.1805692241981732</v>
+        <v>-0.1293841519702939</v>
       </c>
       <c r="E33">
-        <v>-0.1355897630033474</v>
+        <v>-0.1833990485307242</v>
       </c>
       <c r="F33">
-        <v>-0.1140028018707256</v>
+        <v>-0.14132731539492949</v>
       </c>
       <c r="G33">
-        <v>-0.08853019301788768</v>
+        <v>-0.1153777795725576</v>
       </c>
       <c r="H33">
-        <v>-0.1524610618094581</v>
+        <v>-9.9347513074941329E-2</v>
       </c>
       <c r="I33">
-        <v>-0.1174742260544562</v>
+        <v>-0.16348185023935899</v>
       </c>
       <c r="J33">
-        <v>-0.05695712387994504</v>
+        <v>-0.13226190133855709</v>
       </c>
       <c r="K33">
-        <v>0.156910461047403</v>
-      </c>
-      <c r="L33">
-        <v>0.2081470236714941</v>
+        <v>-7.071816985137297E-2</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0.1397640244657854</v>
       </c>
       <c r="M33">
-        <v>0.2400377928718302</v>
+        <v>0.18996911419725859</v>
       </c>
       <c r="N33">
-        <v>0.2616902778732571</v>
+        <v>0.2185019880724802</v>
       </c>
       <c r="O33">
-        <v>0.2735577487026971</v>
+        <v>0.2269616571571795</v>
       </c>
       <c r="P33">
-        <v>0.2797437532114336</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.21931412093480751</v>
+      </c>
+      <c r="Q33">
+        <v>0.2074891728881284</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>-0.06477972953569178</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C34">
-        <v>-0.1202359181252856</v>
+        <v>-6.8855211762843649E-2</v>
       </c>
       <c r="D34">
-        <v>-0.1780635537894117</v>
+        <v>-0.12949919202117821</v>
       </c>
       <c r="E34">
-        <v>-0.136086799783359</v>
+        <v>-0.1847754532629389</v>
       </c>
       <c r="F34">
-        <v>-0.1086013436232022</v>
+        <v>-0.13718487751185779</v>
       </c>
       <c r="G34">
-        <v>-0.0868998561928853</v>
+        <v>-0.1176480392282656</v>
       </c>
       <c r="H34">
-        <v>-0.1542448600861834</v>
+        <v>-9.7632529775008234E-2</v>
       </c>
       <c r="I34">
-        <v>-0.1295109162250175</v>
+        <v>-0.16788320882913971</v>
       </c>
       <c r="J34">
-        <v>-0.07298023806954747</v>
+        <v>-0.12890380732192139</v>
       </c>
       <c r="K34">
-        <v>0.1322908915018153</v>
-      </c>
-      <c r="L34">
-        <v>0.1913387604796715</v>
+        <v>-7.0073649564574264E-2</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0.1219296448991528</v>
       </c>
       <c r="M34">
-        <v>0.2277903447694547</v>
+        <v>0.17893416701723031</v>
       </c>
       <c r="N34">
-        <v>0.2442521896184236</v>
+        <v>0.20899544364395051</v>
       </c>
       <c r="O34">
-        <v>0.2603460709151708</v>
+        <v>0.22848280408630861</v>
       </c>
       <c r="P34">
-        <v>0.2672428206104651</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.22885553074563869</v>
+      </c>
+      <c r="Q34">
+        <v>0.21913537360863669</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>-0.06790359372289741</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C35">
-        <v>-0.1273036036303488</v>
+        <v>-6.8813963016539109E-2</v>
       </c>
       <c r="D35">
-        <v>-0.1834179561283044</v>
+        <v>-0.1202195254136415</v>
       </c>
       <c r="E35">
-        <v>-0.1408448801758455</v>
+        <v>-0.17328306132531049</v>
       </c>
       <c r="F35">
-        <v>-0.1201896392944321</v>
+        <v>-0.13131740724488791</v>
       </c>
       <c r="G35">
-        <v>-0.1013665555359215</v>
+        <v>-0.1102599711451672</v>
       </c>
       <c r="H35">
-        <v>-0.1701584875691323</v>
+        <v>-9.2510106561050603E-2</v>
       </c>
       <c r="I35">
-        <v>-0.1526963503378757</v>
+        <v>-0.16550434432355091</v>
       </c>
       <c r="J35">
-        <v>-0.1028148443600771</v>
+        <v>-0.14002536728150411</v>
       </c>
       <c r="K35">
-        <v>0.09212965610655245</v>
-      </c>
-      <c r="L35">
-        <v>0.1599783713314957</v>
+        <v>-7.8895188556222906E-2</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0.13714318091539299</v>
       </c>
       <c r="M35">
-        <v>0.1984236331966802</v>
+        <v>0.18207000176330021</v>
       </c>
       <c r="N35">
-        <v>0.2325993538599243</v>
+        <v>0.2172169501020384</v>
       </c>
       <c r="O35">
-        <v>0.2462679976127067</v>
+        <v>0.2289306238327192</v>
       </c>
       <c r="P35">
-        <v>0.2724713821490902</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.2275984616563772</v>
+      </c>
+      <c r="Q35">
+        <v>0.2286712040521108</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>-0.0721339185114406</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C36">
-        <v>-0.1351381094511153</v>
+        <v>-6.9401051963059707E-2</v>
       </c>
       <c r="D36">
-        <v>-0.1861796798324897</v>
+        <v>-0.12739609563542539</v>
       </c>
       <c r="E36">
-        <v>-0.1380635306930806</v>
+        <v>-0.1752323047956949</v>
       </c>
       <c r="F36">
-        <v>-0.1213255157727141</v>
+        <v>-0.1342760171207408</v>
       </c>
       <c r="G36">
-        <v>-0.1031196871506868</v>
+        <v>-0.1135693756968526</v>
       </c>
       <c r="H36">
-        <v>-0.1816512023480472</v>
+        <v>-9.5271626867414583E-2</v>
       </c>
       <c r="I36">
-        <v>-0.133657869941571</v>
+        <v>-0.15573047551935421</v>
       </c>
       <c r="J36">
-        <v>-0.06871182882532234</v>
+        <v>-0.12869790045444771</v>
       </c>
       <c r="K36">
-        <v>0.1525699599214737</v>
-      </c>
-      <c r="L36">
-        <v>0.2001574959473308</v>
+        <v>-7.8868720799060724E-2</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0.10347042300664221</v>
       </c>
       <c r="M36">
-        <v>0.2393891922822456</v>
+        <v>0.179207113188038</v>
       </c>
       <c r="N36">
-        <v>0.2476648774921084</v>
+        <v>0.2036573088278506</v>
       </c>
       <c r="O36">
-        <v>0.2357844166244319</v>
+        <v>0.24091566928671809</v>
       </c>
       <c r="P36">
-        <v>0.2179801808868344</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.25269685642156631</v>
+      </c>
+      <c r="Q36">
+        <v>0.28123392102254019</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>-0.06454228510022104</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C37">
-        <v>-0.1170581244658114</v>
+        <v>-0.1175539354686162</v>
       </c>
       <c r="D37">
-        <v>-0.168523030763478</v>
+        <v>-0.19408758984237401</v>
       </c>
       <c r="E37">
-        <v>-0.1286991140679776</v>
+        <v>-0.12001242668167129</v>
       </c>
       <c r="F37">
-        <v>-0.1026973343568724</v>
+        <v>-3.2034150828240723E-2</v>
       </c>
       <c r="G37">
-        <v>-0.08700583672619648</v>
+        <v>-9.9366406258134893E-2</v>
       </c>
       <c r="H37">
-        <v>-0.1526654126139093</v>
+        <v>-4.2715767443932733E-2</v>
       </c>
       <c r="I37">
-        <v>-0.1210936745463852</v>
+        <v>4.7579825462109079E-2</v>
       </c>
       <c r="J37">
-        <v>-0.0602744065687502</v>
+        <v>8.4142327349591789E-2</v>
       </c>
       <c r="K37">
-        <v>0.1549736812785982</v>
+        <v>7.8542428458030958E-2</v>
       </c>
       <c r="L37">
-        <v>0.2009921909146428</v>
+        <v>8.4728020576492577E-2</v>
       </c>
       <c r="M37">
-        <v>0.2350732631338469</v>
+        <v>7.4420679216229857E-2</v>
       </c>
       <c r="N37">
-        <v>0.2383605441085981</v>
+        <v>3.1951043030654859E-2</v>
       </c>
       <c r="O37">
-        <v>0.2339551979577682</v>
+        <v>5.471005829846378E-2</v>
       </c>
       <c r="P37">
-        <v>0.2150009197595915</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>5.5359573737743847E-2</v>
+      </c>
+      <c r="Q37">
+        <v>5.630439708252076E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>-0.06840291074110766</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C38">
-        <v>-0.1240253908900542</v>
+        <v>-9.0468185548435304E-2</v>
       </c>
       <c r="D38">
-        <v>-0.1757527072770098</v>
+        <v>-0.17331253967012181</v>
       </c>
       <c r="E38">
-        <v>-0.1260678251495131</v>
+        <v>-0.1434707399930758</v>
       </c>
       <c r="F38">
-        <v>-0.1042532588916723</v>
+        <v>5.4753943733241196E-3</v>
       </c>
       <c r="G38">
-        <v>-0.08192876986831368</v>
-      </c>
-      <c r="H38">
-        <v>-0.1414770221243415</v>
+        <v>3.017413303385446E-2</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.15316216711699379</v>
       </c>
       <c r="I38">
-        <v>-0.1153480303952312</v>
+        <v>0.27572866078807551</v>
       </c>
       <c r="J38">
-        <v>-0.05413327439363098</v>
+        <v>0.27391849807032942</v>
       </c>
       <c r="K38">
-        <v>0.1506842528625266</v>
+        <v>0.2360526929203787</v>
       </c>
       <c r="L38">
-        <v>0.1989662170504575</v>
+        <v>0.19787789111839951</v>
       </c>
       <c r="M38">
-        <v>0.2298094633009644</v>
+        <v>0.19181526409789471</v>
       </c>
       <c r="N38">
-        <v>0.2416132513100508</v>
+        <v>0.18133114871741199</v>
       </c>
       <c r="O38">
-        <v>0.2509670477103361</v>
+        <v>0.18391515336324091</v>
       </c>
       <c r="P38">
-        <v>0.2307279913714483</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.1986089856150571</v>
+      </c>
+      <c r="Q38">
+        <v>0.20695635302227949</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>-0.07056549107845414</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C39">
-        <v>-0.1285210767342237</v>
+        <v>-8.5336246490704468E-2</v>
       </c>
       <c r="D39">
-        <v>-0.1809159051540843</v>
+        <v>-0.1589941323337766</v>
       </c>
       <c r="E39">
-        <v>-0.1384791670646802</v>
+        <v>-0.1192277591023872</v>
       </c>
       <c r="F39">
-        <v>-0.1113555858077294</v>
+        <v>8.2234166630224398E-3</v>
       </c>
       <c r="G39">
-        <v>-0.09427409692311646</v>
-      </c>
-      <c r="H39">
-        <v>-0.1604388020159296</v>
+        <v>1.080875580467687E-2</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0.1203137534243368</v>
       </c>
       <c r="I39">
-        <v>-0.1280778490391066</v>
+        <v>0.2449264373844148</v>
       </c>
       <c r="J39">
-        <v>-0.06580792466901621</v>
+        <v>0.23673034667195941</v>
       </c>
       <c r="K39">
-        <v>0.1405305281617079</v>
+        <v>0.24509777079502751</v>
       </c>
       <c r="L39">
-        <v>0.1864114933886937</v>
+        <v>0.2379521074198018</v>
       </c>
       <c r="M39">
-        <v>0.2232575210656444</v>
+        <v>0.21896378850475831</v>
       </c>
       <c r="N39">
-        <v>0.2334214865097468</v>
+        <v>0.23996265588138579</v>
       </c>
       <c r="O39">
-        <v>0.238274921913969</v>
+        <v>0.22353311109204599</v>
       </c>
       <c r="P39">
-        <v>0.2251361479085532</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.20998559843243919</v>
+      </c>
+      <c r="Q39">
+        <v>0.21574131726647011</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>-0.0700839122959018</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C40">
-        <v>-0.1246390809867833</v>
+        <v>-0.10616119317134209</v>
       </c>
       <c r="D40">
-        <v>-0.1746652881136436</v>
+        <v>-7.7592299444609325E-2</v>
       </c>
       <c r="E40">
-        <v>-0.1315818480630474</v>
+        <v>-7.5792489616482615E-4</v>
       </c>
       <c r="F40">
-        <v>-0.1114689274671426</v>
+        <v>-2.5390698579601391E-2</v>
       </c>
       <c r="G40">
-        <v>-0.0915712203027407</v>
+        <v>9.6014915333048262E-2</v>
       </c>
       <c r="H40">
-        <v>-0.1539180825266185</v>
-      </c>
-      <c r="I40">
-        <v>-0.1265828903320221</v>
+        <v>0.15673446745269529</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0.1569208148044462</v>
       </c>
       <c r="J40">
-        <v>-0.07101044696594994</v>
+        <v>0.11724822553668381</v>
       </c>
       <c r="K40">
-        <v>0.1193249762433049</v>
+        <v>0.1192720057202226</v>
       </c>
       <c r="L40">
-        <v>0.180693923533164</v>
+        <v>0.15506423597339239</v>
       </c>
       <c r="M40">
-        <v>0.2126597009920081</v>
+        <v>0.14787436812908961</v>
       </c>
       <c r="N40">
-        <v>0.2443278447232468</v>
+        <v>0.16621807005252531</v>
       </c>
       <c r="O40">
-        <v>0.2574297301517036</v>
+        <v>0.14929871768945371</v>
       </c>
       <c r="P40">
-        <v>0.2853069982783915</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.1196870716000647</v>
+      </c>
+      <c r="Q40">
+        <v>5.5571810564084632E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>-0.1127519278908456</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C41">
-        <v>-0.1845773529806243</v>
+        <v>-0.1164723144882223</v>
       </c>
       <c r="D41">
-        <v>-0.1184118162536125</v>
+        <v>-0.26597461324775701</v>
       </c>
       <c r="E41">
-        <v>-0.03027874800478106</v>
+        <v>-0.17348880203750219</v>
       </c>
       <c r="F41">
-        <v>-0.09083468429934188</v>
+        <v>-0.17069972490826771</v>
       </c>
       <c r="G41">
-        <v>-0.03910743668687493</v>
+        <v>-8.893233550147453E-2</v>
       </c>
       <c r="H41">
-        <v>0.05673137510353977</v>
+        <v>-7.2017027146971072E-2</v>
       </c>
       <c r="I41">
-        <v>0.09344685230918122</v>
+        <v>-4.3450693824968752E-2</v>
       </c>
       <c r="J41">
-        <v>0.08805539735379704</v>
+        <v>3.8976088728526221E-3</v>
       </c>
       <c r="K41">
-        <v>0.09597523839040585</v>
+        <v>-3.4162224695663802E-2</v>
       </c>
       <c r="L41">
-        <v>0.07856245089623948</v>
+        <v>-6.3573828818924275E-2</v>
       </c>
       <c r="M41">
-        <v>0.03635912311581361</v>
+        <v>-6.5202853364924249E-2</v>
       </c>
       <c r="N41">
-        <v>0.05804176653358017</v>
+        <v>-8.6423706699215619E-2</v>
       </c>
       <c r="O41">
-        <v>0.06104655999312922</v>
+        <v>-0.1387459552174676</v>
       </c>
       <c r="P41">
-        <v>0.06051774178650015</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>-0.1456562348845773</v>
+      </c>
+      <c r="Q41">
+        <v>-0.15975210524660749</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>-0.08440044907419662</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C42">
-        <v>-0.1675190824107607</v>
+        <v>-2.4079129103167521E-2</v>
       </c>
       <c r="D42">
-        <v>-0.1398854879172393</v>
+        <v>-0.31885267084009772</v>
       </c>
       <c r="E42">
-        <v>0.006924536900875451</v>
+        <v>-0.19611721182558511</v>
       </c>
       <c r="F42">
-        <v>0.02751265382431366</v>
+        <v>4.7060746188968577E-2</v>
       </c>
       <c r="G42">
-        <v>0.1520614114160024</v>
-      </c>
-      <c r="H42">
-        <v>0.2694625255723069</v>
+        <v>0.1229690818531753</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0.172588940126745</v>
       </c>
       <c r="I42">
-        <v>0.2674576804399398</v>
+        <v>0.25790387732600972</v>
       </c>
       <c r="J42">
-        <v>0.2262830983381857</v>
+        <v>0.26902268604335328</v>
       </c>
       <c r="K42">
-        <v>0.182329053233986</v>
+        <v>0.2468139738700367</v>
       </c>
       <c r="L42">
-        <v>0.1772643719741784</v>
+        <v>0.26911413612907692</v>
       </c>
       <c r="M42">
-        <v>0.1641928142385302</v>
+        <v>0.26596213009884812</v>
       </c>
       <c r="N42">
-        <v>0.1722982993747067</v>
+        <v>0.24879965921958169</v>
       </c>
       <c r="O42">
-        <v>0.1913391762330252</v>
+        <v>0.24120905378712901</v>
       </c>
       <c r="P42">
-        <v>0.20324972746184</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.24648529336658409</v>
+      </c>
+      <c r="Q42">
+        <v>0.2291626243901593</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>-0.08597604976404592</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C43">
-        <v>-0.1546324534342997</v>
+        <v>-6.9897652745686184E-2</v>
       </c>
       <c r="D43">
-        <v>-0.1149410956345631</v>
+        <v>-0.11434416288305101</v>
       </c>
       <c r="E43">
-        <v>-0.0008803011178761527</v>
+        <v>-1.050785869509642E-2</v>
       </c>
       <c r="F43">
-        <v>0.009961905302081879</v>
-      </c>
-      <c r="G43">
-        <v>0.1131506245529324</v>
+        <v>2.7003765047599292E-2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.17856656190608899</v>
       </c>
       <c r="H43">
-        <v>0.2462991809072787</v>
+        <v>0.23180627375430499</v>
       </c>
       <c r="I43">
-        <v>0.2382626887641738</v>
+        <v>0.26251075681529612</v>
       </c>
       <c r="J43">
-        <v>0.2452430414473567</v>
+        <v>0.25470903299200931</v>
       </c>
       <c r="K43">
-        <v>0.2361838302333045</v>
+        <v>0.2205984990880073</v>
       </c>
       <c r="L43">
-        <v>0.2284034506572805</v>
+        <v>0.26179585040142411</v>
       </c>
       <c r="M43">
-        <v>0.2445248373235853</v>
+        <v>0.26491160214751108</v>
       </c>
       <c r="N43">
-        <v>0.2331139510721608</v>
+        <v>0.26635803722964457</v>
       </c>
       <c r="O43">
-        <v>0.2150877334648114</v>
+        <v>0.25131626953869313</v>
       </c>
       <c r="P43">
-        <v>0.2208504471999506</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>-0.1166150191957295</v>
-      </c>
-      <c r="C44">
-        <v>-0.08568569649923764</v>
-      </c>
-      <c r="D44">
-        <v>0.004241334884028243</v>
-      </c>
-      <c r="E44">
-        <v>-0.02672946074656913</v>
-      </c>
-      <c r="F44">
-        <v>0.09349631760754622</v>
-      </c>
-      <c r="G44">
-        <v>0.1589402298102577</v>
-      </c>
-      <c r="H44">
-        <v>0.1531402466899255</v>
-      </c>
-      <c r="I44">
-        <v>0.1142779581220504</v>
-      </c>
-      <c r="J44">
-        <v>0.1091444274164672</v>
-      </c>
-      <c r="K44">
-        <v>0.1454036879137125</v>
-      </c>
-      <c r="L44">
-        <v>0.1345505032154249</v>
-      </c>
-      <c r="M44">
-        <v>0.149137520801843</v>
-      </c>
-      <c r="N44">
-        <v>0.1305526886593854</v>
-      </c>
-      <c r="O44">
-        <v>0.1014556306136796</v>
-      </c>
-      <c r="P44">
-        <v>0.04702939450096722</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>-0.116874542353285</v>
-      </c>
-      <c r="C45">
-        <v>-0.2878704572774626</v>
-      </c>
-      <c r="D45">
-        <v>-0.187799904839801</v>
-      </c>
-      <c r="E45">
-        <v>-0.1827139760012107</v>
-      </c>
-      <c r="F45">
-        <v>-0.1094907254695902</v>
-      </c>
-      <c r="G45">
-        <v>-0.08701596080538532</v>
-      </c>
-      <c r="H45">
-        <v>-0.06740292888462757</v>
-      </c>
-      <c r="I45">
-        <v>-0.02205119611961466</v>
-      </c>
-      <c r="J45">
-        <v>-0.04786607318354285</v>
-      </c>
-      <c r="K45">
-        <v>-0.08034205116146179</v>
-      </c>
-      <c r="L45">
-        <v>-0.07656221969087956</v>
-      </c>
-      <c r="M45">
-        <v>-0.09775330883981487</v>
-      </c>
-      <c r="N45">
-        <v>-0.1516917517577817</v>
-      </c>
-      <c r="O45">
-        <v>-0.1604993568501384</v>
-      </c>
-      <c r="P45">
-        <v>-0.1807044947349789</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>-0.01943771833120425</v>
-      </c>
-      <c r="C46">
-        <v>-0.2994513016716448</v>
-      </c>
-      <c r="D46">
-        <v>-0.1637327707003554</v>
-      </c>
-      <c r="E46">
-        <v>0.06748415787772544</v>
-      </c>
-      <c r="F46">
-        <v>0.1315146608101443</v>
-      </c>
-      <c r="G46">
-        <v>0.1766658110622349</v>
-      </c>
-      <c r="H46">
-        <v>0.2610426336871491</v>
-      </c>
-      <c r="I46">
-        <v>0.2687420795085386</v>
-      </c>
-      <c r="J46">
-        <v>0.2531381398036315</v>
-      </c>
-      <c r="K46">
-        <v>0.274631149011539</v>
-      </c>
-      <c r="L46">
-        <v>0.2689749068005968</v>
-      </c>
-      <c r="M46">
-        <v>0.2480267432609486</v>
-      </c>
-      <c r="N46">
-        <v>0.2435731624676962</v>
-      </c>
-      <c r="O46">
-        <v>0.2436665003420025</v>
-      </c>
-      <c r="P46">
-        <v>0.2261691810490172</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>-0.07951112901220368</v>
-      </c>
-      <c r="C47">
-        <v>-0.1261401422125007</v>
-      </c>
-      <c r="D47">
-        <v>-0.02653928998160525</v>
-      </c>
-      <c r="E47">
-        <v>0.005104004100516939</v>
-      </c>
-      <c r="F47">
-        <v>0.1722873209920883</v>
-      </c>
-      <c r="G47">
-        <v>0.2197105970503698</v>
-      </c>
-      <c r="H47">
-        <v>0.2591090234908717</v>
-      </c>
-      <c r="I47">
-        <v>0.2463352691423424</v>
-      </c>
-      <c r="J47">
-        <v>0.2146271440582258</v>
-      </c>
-      <c r="K47">
-        <v>0.2483973378590129</v>
-      </c>
-      <c r="L47">
-        <v>0.2491990064580432</v>
-      </c>
-      <c r="M47">
-        <v>0.2495246518748517</v>
-      </c>
-      <c r="N47">
-        <v>0.2274615478490895</v>
-      </c>
-      <c r="O47">
-        <v>0.2108466063230615</v>
-      </c>
-      <c r="P47">
-        <v>0.1858888790251589</v>
+        <v>0.23205392819497389</v>
+      </c>
+      <c r="Q43">
+        <v>0.21436188250370569</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:Q43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>